--- a/Source/arkD - 副本.xlsx
+++ b/Source/arkD - 副本.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="6_{05AF7F78-DF39-446C-B1A9-C9994B7B3EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="13320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3017" yWindow="3017" windowWidth="24592" windowHeight="10217" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="其他信息" sheetId="2" r:id="rId1"/>

--- a/Source/arkD - 副本.xlsx
+++ b/Source/arkD - 副本.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37b141e1e60375e0/Arknights/ArknightsIDcard-Ebranch/ArknightsIDCard/Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{05AF7F78-DF39-446C-B1A9-C9994B7B3EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{CEBBFEC2-EB42-4FE1-B0B7-F54EA67B262D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3017" yWindow="3017" windowWidth="24592" windowHeight="10217" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="14620" windowHeight="25220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="其他信息" sheetId="2" r:id="rId1"/>
     <sheet name="练度表" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$269</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="254">
   <si>
     <t>陈</t>
   </si>
@@ -496,385 +496,419 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>HOK-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMB-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin3</t>
+  </si>
+  <si>
+    <t>ARC-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛恩纳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRO-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRO-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四五星三技能填0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不填则随机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白铁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOL-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOL-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伺夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斥罪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缄默德克萨斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUM-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焰影苇草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCR-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仇白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麒麟X夜刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUS-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊内丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLX-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRP-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缪尔赛思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霍尔海雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淬羽赫默</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOM-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UMD-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣约送葬人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提丰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琳琅诗怀雅</t>
+  </si>
+  <si>
+    <t>MER-X</t>
+  </si>
+  <si>
+    <t>CEN-X</t>
+  </si>
+  <si>
+    <t>REA-X</t>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉</t>
+  </si>
+  <si>
+    <t>涤火杰西卡</t>
+  </si>
+  <si>
+    <t>BLS-X</t>
+  </si>
+  <si>
+    <t>赫德雷</t>
+  </si>
+  <si>
+    <t>FOR-X</t>
+  </si>
+  <si>
+    <t>ARC-X</t>
+  </si>
+  <si>
+    <t>薇薇安娜</t>
+  </si>
+  <si>
+    <t>止颂</t>
+  </si>
+  <si>
+    <t>UNY-X</t>
+  </si>
+  <si>
+    <t>塑心</t>
+  </si>
+  <si>
+    <t>锏</t>
+  </si>
+  <si>
+    <t>FUN-X</t>
+  </si>
+  <si>
+    <t>INC-X</t>
+  </si>
+  <si>
+    <t>DEC-Y</t>
+  </si>
+  <si>
+    <t>莱伊</t>
+  </si>
+  <si>
+    <t>FGT-Y</t>
+  </si>
+  <si>
+    <t>FGT-X</t>
+  </si>
+  <si>
+    <t>左乐</t>
+  </si>
+  <si>
+    <t>黍</t>
+  </si>
+  <si>
+    <t>SBL-X</t>
+  </si>
+  <si>
+    <t>GUA-X</t>
+  </si>
+  <si>
+    <t>SPT-X</t>
+  </si>
+  <si>
+    <t>艾拉</t>
+  </si>
+  <si>
+    <t>TRP-Δ</t>
+  </si>
+  <si>
+    <t>TAC-X</t>
+  </si>
+  <si>
+    <t>阿斯卡纶</t>
+  </si>
+  <si>
+    <t>LOR-X</t>
+  </si>
+  <si>
+    <t>维什戴尔</t>
+  </si>
+  <si>
+    <t>BOM-X</t>
+  </si>
+  <si>
+    <t>逻各斯</t>
+  </si>
+  <si>
+    <t>魔王</t>
+  </si>
+  <si>
+    <t>CCR-X</t>
+  </si>
+  <si>
+    <t>CCR-Δ</t>
+  </si>
+  <si>
+    <t>乌尔比安</t>
+  </si>
+  <si>
+    <t>HUN-X</t>
+  </si>
+  <si>
+    <t>2019.05.06</t>
+  </si>
+  <si>
+    <t>妮芙</t>
+  </si>
+  <si>
+    <t>RPR-X</t>
+  </si>
+  <si>
+    <t>忍冬</t>
+  </si>
+  <si>
+    <t>佩佩</t>
+  </si>
+  <si>
+    <t>娜仁图亚</t>
+  </si>
+  <si>
+    <t>荒芜拉普兰德</t>
+  </si>
+  <si>
+    <t>玛露西尔</t>
+  </si>
+  <si>
+    <t>WAH-X</t>
+  </si>
+  <si>
+    <t>弑君者</t>
+  </si>
+  <si>
+    <t>引星棘刺</t>
+  </si>
+  <si>
+    <t>SOL-X</t>
+  </si>
+  <si>
+    <t>BAR-X</t>
+  </si>
+  <si>
+    <t>RIT-X</t>
+  </si>
+  <si>
+    <t>WDM-X</t>
+  </si>
+  <si>
+    <t>CRU-X</t>
+  </si>
+  <si>
+    <t>AFT-X</t>
+  </si>
+  <si>
+    <t>维娜·维多利亚</t>
+  </si>
+  <si>
+    <t>AFT-Δ</t>
+  </si>
+  <si>
+    <t>ISW-A</t>
+  </si>
+  <si>
+    <t>HAM-X</t>
+  </si>
+  <si>
+    <t>RA-A</t>
+  </si>
+  <si>
+    <t>余</t>
+  </si>
+  <si>
+    <t>BLA-D</t>
+  </si>
+  <si>
+    <t>烛煌</t>
+  </si>
+  <si>
+    <t>PUS-Y</t>
+  </si>
+  <si>
+    <t>2025.05.02</t>
+  </si>
+  <si>
+    <t>BEA-Y</t>
+  </si>
+  <si>
+    <t>AGE-Y</t>
+  </si>
+  <si>
+    <t>重岳</t>
+  </si>
+  <si>
+    <t>LIB-X</t>
+  </si>
+  <si>
+    <t>隐德来希</t>
+  </si>
+  <si>
+    <t>信仰搅拌机</t>
+  </si>
+  <si>
     <t>鸿雪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HOK-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMB-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skin3</t>
-  </si>
-  <si>
-    <t>ARC-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛恩纳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRO-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRO-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>四五星三技能填0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不填则随机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模组名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模组等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白铁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOL-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOL-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伺夜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斥罪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缄默德克萨斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUM-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SIE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>焰影苇草</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重岳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCR-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仇白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麒麟X夜刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUS-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伊内丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLX-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRP-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缪尔赛思</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>霍尔海雅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淬羽赫默</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BOM-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UMD-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣约送葬人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CRA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蕾缪安</t>
+  </si>
+  <si>
+    <t>DEA-Y</t>
+  </si>
+  <si>
+    <t>死芒</t>
+  </si>
+  <si>
+    <t>Mon3tr</t>
+  </si>
+  <si>
+    <t>新约能天使</t>
   </si>
   <si>
     <t>GEE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BEA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提丰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SIE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琳琅诗怀雅</t>
-  </si>
-  <si>
-    <t>MER-X</t>
-  </si>
-  <si>
-    <t>CEN-X</t>
-  </si>
-  <si>
-    <t>REA-X</t>
-  </si>
-  <si>
-    <t>纯烬艾雅法拉</t>
-  </si>
-  <si>
-    <t>涤火杰西卡</t>
-  </si>
-  <si>
-    <t>BLS-X</t>
-  </si>
-  <si>
-    <t>赫德雷</t>
-  </si>
-  <si>
-    <t>FOR-X</t>
-  </si>
-  <si>
-    <t>ARC-X</t>
-  </si>
-  <si>
-    <t>薇薇安娜</t>
-  </si>
-  <si>
-    <t>止颂</t>
-  </si>
-  <si>
-    <t>UNY-X</t>
-  </si>
-  <si>
-    <t>塑心</t>
-  </si>
-  <si>
-    <t>锏</t>
-  </si>
-  <si>
-    <t>FUN-X</t>
-  </si>
-  <si>
-    <t>INC-X</t>
-  </si>
-  <si>
-    <t>DEC-Y</t>
-  </si>
-  <si>
-    <t>莱伊</t>
-  </si>
-  <si>
-    <t>FGT-Y</t>
-  </si>
-  <si>
-    <t>FGT-X</t>
-  </si>
-  <si>
-    <t>左乐</t>
-  </si>
-  <si>
-    <t>黍</t>
-  </si>
-  <si>
-    <t>SBL-X</t>
-  </si>
-  <si>
-    <t>GUA-X</t>
-  </si>
-  <si>
-    <t>SPT-X</t>
-  </si>
-  <si>
-    <t>艾拉</t>
-  </si>
-  <si>
-    <t>TRP-Δ</t>
-  </si>
-  <si>
-    <t>TAC-X</t>
-  </si>
-  <si>
-    <t>阿斯卡纶</t>
-  </si>
-  <si>
-    <t>LOR-X</t>
-  </si>
-  <si>
-    <t>维什戴尔</t>
-  </si>
-  <si>
-    <t>BOM-X</t>
-  </si>
-  <si>
-    <t>逻各斯</t>
-  </si>
-  <si>
-    <t>魔王</t>
-  </si>
-  <si>
-    <t>CCR-X</t>
-  </si>
-  <si>
-    <t>CCR-Δ</t>
-  </si>
-  <si>
-    <t>乌尔比安</t>
-  </si>
-  <si>
-    <t>HUN-X</t>
-  </si>
-  <si>
-    <t>2019.05.06</t>
-  </si>
-  <si>
-    <t>妮芙</t>
-  </si>
-  <si>
-    <t>RPR-X</t>
-  </si>
-  <si>
-    <t>忍冬</t>
-  </si>
-  <si>
-    <t>佩佩</t>
-  </si>
-  <si>
-    <t>娜仁图亚</t>
-  </si>
-  <si>
-    <t>荒芜拉普兰德</t>
-  </si>
-  <si>
-    <t>玛露西尔</t>
-  </si>
-  <si>
-    <t>WAH-X</t>
-  </si>
-  <si>
-    <t>弑君者</t>
-  </si>
-  <si>
-    <t>引星棘刺</t>
-  </si>
-  <si>
-    <t>SOL-X</t>
-  </si>
-  <si>
-    <t>BAR-X</t>
-  </si>
-  <si>
-    <t>RIT-X</t>
-  </si>
-  <si>
-    <t>WDM-X</t>
-  </si>
-  <si>
-    <t>CRU-X</t>
-  </si>
-  <si>
-    <t>AFT-X</t>
-  </si>
-  <si>
-    <t>维娜·维多利亚</t>
-  </si>
-  <si>
-    <t>AFT-Δ</t>
-  </si>
-  <si>
-    <t>ISW-A</t>
-  </si>
-  <si>
-    <t>HAM-X</t>
-  </si>
-  <si>
-    <t>RA-A</t>
-  </si>
-  <si>
-    <t>余</t>
-  </si>
-  <si>
-    <t>BLA-D</t>
-  </si>
-  <si>
-    <t>烛煌</t>
-  </si>
-  <si>
-    <t>PUS-Y</t>
-  </si>
-  <si>
-    <t>2025.02.13</t>
+  </si>
+  <si>
+    <t>ALC-X</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1368,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1342,7 +1376,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1358,7 +1392,7 @@
         <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1456,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="19.15234375" customWidth="1"/>
@@ -1475,7 +1509,7 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12"/>
       <c r="F1" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
@@ -1483,13 +1517,13 @@
         <v>55</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="L1" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1597,7 +1631,7 @@
         <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1646,7 +1680,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -1670,10 +1704,10 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -1708,10 +1742,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K7">
         <v>3</v>
@@ -1722,13 +1756,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1746,27 +1780,27 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1784,10 +1818,10 @@
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J9" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1798,7 +1832,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1822,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1836,13 +1870,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1860,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J11" t="s">
         <v>145</v>
@@ -1869,18 +1903,18 @@
         <v>1</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1900,10 +1934,19 @@
       <c r="I12" t="s">
         <v>57</v>
       </c>
+      <c r="J12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -1930,24 +1973,24 @@
         <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1965,10 +2008,10 @@
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1979,7 +2022,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -2003,10 +2046,10 @@
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J15" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2017,13 +2060,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2044,7 +2087,7 @@
         <v>58</v>
       </c>
       <c r="J16" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2055,13 +2098,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2079,27 +2122,27 @@
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J17" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
         <v>1</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2120,24 +2163,24 @@
         <v>57</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2158,18 +2201,18 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -2196,10 +2239,10 @@
         <v>58</v>
       </c>
       <c r="J20" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>105</v>
@@ -2207,13 +2250,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2231,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J21" t="s">
         <v>83</v>
@@ -2245,13 +2288,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2269,18 +2312,27 @@
         <v>10</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J22" t="s">
+        <v>204</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2298,27 +2350,27 @@
         <v>10</v>
       </c>
       <c r="I23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>219</v>
+        <v>4</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2336,13 +2388,13 @@
         <v>10</v>
       </c>
       <c r="I24" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J24" t="s">
-        <v>235</v>
+        <v>84</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>105</v>
@@ -2350,14 +2402,14 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25">
         <v>5</v>
       </c>
-      <c r="B25">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
       <c r="D25">
         <v>2</v>
       </c>
@@ -2374,13 +2426,13 @@
         <v>10</v>
       </c>
       <c r="I25" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J25" t="s">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>105</v>
@@ -2388,7 +2440,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -2412,21 +2464,21 @@
         <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J26" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="K26">
         <v>1</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -2453,10 +2505,10 @@
         <v>58</v>
       </c>
       <c r="J27" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>105</v>
@@ -2464,13 +2516,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -2491,18 +2543,18 @@
         <v>57</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>6</v>
@@ -2529,24 +2581,24 @@
         <v>58</v>
       </c>
       <c r="J29" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="K29">
         <v>3</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>7</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -2564,10 +2616,10 @@
         <v>10</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J30" t="s">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -2578,13 +2630,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2602,27 +2654,27 @@
         <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J31" t="s">
-        <v>231</v>
+        <v>104</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2643,24 +2695,24 @@
         <v>109</v>
       </c>
       <c r="J32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2681,7 +2733,7 @@
         <v>57</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -2692,13 +2744,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="B34">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2716,21 +2768,21 @@
         <v>10</v>
       </c>
       <c r="I34" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J34" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -2768,13 +2820,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2792,27 +2844,27 @@
         <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J36" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -2830,21 +2882,21 @@
         <v>10</v>
       </c>
       <c r="I37" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="J37" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K37">
         <v>3</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -2868,27 +2920,27 @@
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J38" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="K38">
         <v>3</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2909,24 +2961,24 @@
         <v>57</v>
       </c>
       <c r="J39" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="B40">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2944,27 +2996,27 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>179</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2982,27 +3034,27 @@
         <v>10</v>
       </c>
       <c r="I41" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="J41" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -3020,27 +3072,27 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="K42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3058,21 +3110,21 @@
         <v>10</v>
       </c>
       <c r="I43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J43" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="K43">
         <v>2</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3096,21 +3148,21 @@
         <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="J44" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -3137,10 +3189,10 @@
         <v>57</v>
       </c>
       <c r="J45" t="s">
-        <v>236</v>
+        <v>86</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>107</v>
@@ -3148,13 +3200,13 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>198</v>
+        <v>67</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -3172,21 +3224,21 @@
         <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J46" t="s">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B47">
         <v>6</v>
@@ -3213,24 +3265,24 @@
         <v>57</v>
       </c>
       <c r="J47" t="s">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -3251,53 +3303,62 @@
         <v>57</v>
       </c>
       <c r="J48" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>237</v>
+        <v>68</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>90</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>57</v>
+      </c>
+      <c r="J49" t="s">
+        <v>88</v>
+      </c>
+      <c r="K49">
         <v>1</v>
       </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49">
-        <v>90</v>
-      </c>
-      <c r="F49">
-        <v>10</v>
-      </c>
-      <c r="G49">
-        <v>10</v>
-      </c>
-      <c r="H49">
-        <v>10</v>
-      </c>
-      <c r="I49" t="s">
-        <v>109</v>
+      <c r="L49" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -3318,24 +3379,24 @@
         <v>57</v>
       </c>
       <c r="J50" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="K50">
         <v>1</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -3344,36 +3405,36 @@
         <v>90</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I51" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J51" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>235</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -3391,27 +3452,18 @@
         <v>10</v>
       </c>
       <c r="I52" t="s">
-        <v>57</v>
-      </c>
-      <c r="J52" t="s">
-        <v>185</v>
-      </c>
-      <c r="K52">
-        <v>3</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -3432,10 +3484,10 @@
         <v>58</v>
       </c>
       <c r="J53" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>105</v>
@@ -3443,13 +3495,13 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -3470,24 +3522,24 @@
         <v>57</v>
       </c>
       <c r="J54" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="K54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3505,13 +3557,13 @@
         <v>10</v>
       </c>
       <c r="I55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J55" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>105</v>
@@ -3519,13 +3571,13 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>246</v>
       </c>
       <c r="B56">
         <v>6</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -3546,10 +3598,10 @@
         <v>57</v>
       </c>
       <c r="J56" t="s">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>105</v>
@@ -3557,13 +3609,13 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3587,7 +3639,7 @@
         <v>126</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>105</v>
@@ -3595,13 +3647,13 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="B58">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -3622,24 +3674,24 @@
         <v>57</v>
       </c>
       <c r="J58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K58">
         <v>3</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -3657,13 +3709,13 @@
         <v>10</v>
       </c>
       <c r="I59" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J59" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>105</v>
@@ -3671,13 +3723,13 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3695,27 +3747,27 @@
         <v>10</v>
       </c>
       <c r="I60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J60" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K60">
         <v>3</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -3733,18 +3785,27 @@
         <v>10</v>
       </c>
       <c r="I61" t="s">
-        <v>109</v>
+        <v>57</v>
+      </c>
+      <c r="J61" t="s">
+        <v>212</v>
+      </c>
+      <c r="K61">
+        <v>3</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3753,19 +3814,19 @@
         <v>90</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="J62" t="s">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -3776,7 +3837,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>174</v>
+        <v>14</v>
       </c>
       <c r="B63">
         <v>6</v>
@@ -3800,13 +3861,13 @@
         <v>10</v>
       </c>
       <c r="I63" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J63" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>105</v>
@@ -3814,13 +3875,13 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -3838,21 +3899,21 @@
         <v>10</v>
       </c>
       <c r="I64" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J64" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>218</v>
       </c>
       <c r="B65">
         <v>6</v>
@@ -3876,27 +3937,18 @@
         <v>10</v>
       </c>
       <c r="I65" t="s">
-        <v>57</v>
-      </c>
-      <c r="J65" t="s">
-        <v>91</v>
-      </c>
-      <c r="K65">
-        <v>2</v>
-      </c>
-      <c r="L65" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3914,13 +3966,13 @@
         <v>10</v>
       </c>
       <c r="I66" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="J66" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>105</v>
@@ -3928,13 +3980,13 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="B67">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3952,10 +4004,10 @@
         <v>10</v>
       </c>
       <c r="I67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J67" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="K67">
         <v>3</v>
@@ -3966,13 +4018,13 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3990,13 +4042,13 @@
         <v>10</v>
       </c>
       <c r="I68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J68" t="s">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>105</v>
@@ -4004,13 +4056,13 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="B69">
         <v>6</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -4031,10 +4083,10 @@
         <v>57</v>
       </c>
       <c r="J69" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>105</v>
@@ -4042,13 +4094,13 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -4066,13 +4118,13 @@
         <v>10</v>
       </c>
       <c r="I70" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J70" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>105</v>
@@ -4080,13 +4132,13 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4107,10 +4159,10 @@
         <v>57</v>
       </c>
       <c r="J71" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>105</v>
@@ -4118,7 +4170,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B72">
         <v>6</v>
@@ -4142,21 +4194,21 @@
         <v>10</v>
       </c>
       <c r="I72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J72" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="K72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B73">
         <v>6</v>
@@ -4180,10 +4232,10 @@
         <v>10</v>
       </c>
       <c r="I73" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J73" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="K73">
         <v>3</v>
@@ -4194,13 +4246,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -4221,18 +4273,18 @@
         <v>57</v>
       </c>
       <c r="J74" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B75">
         <v>6</v>
@@ -4259,7 +4311,7 @@
         <v>109</v>
       </c>
       <c r="J75" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="K75">
         <v>3</v>
@@ -4270,13 +4322,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="B76">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4294,21 +4346,21 @@
         <v>10</v>
       </c>
       <c r="I76" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J76" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B77">
         <v>6</v>
@@ -4332,27 +4384,27 @@
         <v>10</v>
       </c>
       <c r="I77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J77" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="B78">
         <v>6</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4370,18 +4422,27 @@
         <v>10</v>
       </c>
       <c r="I78" t="s">
-        <v>109</v>
+        <v>58</v>
+      </c>
+      <c r="J78" t="s">
+        <v>209</v>
+      </c>
+      <c r="K78">
+        <v>3</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="B79">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4402,24 +4463,24 @@
         <v>57</v>
       </c>
       <c r="J79" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="B80">
         <v>6</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -4440,24 +4501,24 @@
         <v>57</v>
       </c>
       <c r="J80" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="K80">
         <v>3</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>220</v>
       </c>
       <c r="B81">
         <v>6</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -4478,18 +4539,18 @@
         <v>57</v>
       </c>
       <c r="J81" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="K81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B82">
         <v>6</v>
@@ -4516,24 +4577,24 @@
         <v>58</v>
       </c>
       <c r="J82" t="s">
-        <v>238</v>
+        <v>93</v>
       </c>
       <c r="K82">
         <v>3</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="B83">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -4553,25 +4614,16 @@
       <c r="I83" t="s">
         <v>57</v>
       </c>
-      <c r="J83" t="s">
-        <v>95</v>
-      </c>
-      <c r="K83">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B84">
         <v>6</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4594,13 +4646,13 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="B85">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4621,24 +4673,24 @@
         <v>57</v>
       </c>
       <c r="J85" t="s">
-        <v>229</v>
+        <v>94</v>
       </c>
       <c r="K85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B86">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -4656,13 +4708,13 @@
         <v>10</v>
       </c>
       <c r="I86" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J86" t="s">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>107</v>
@@ -4670,7 +4722,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B87">
         <v>6</v>
@@ -4697,18 +4749,18 @@
         <v>57</v>
       </c>
       <c r="J87" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B88">
         <v>6</v>
@@ -4732,10 +4784,10 @@
         <v>10</v>
       </c>
       <c r="I88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K88">
         <v>3</v>
@@ -4746,13 +4798,13 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="B89">
         <v>6</v>
       </c>
       <c r="C89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4773,24 +4825,24 @@
         <v>57</v>
       </c>
       <c r="J89" t="s">
-        <v>223</v>
+        <v>95</v>
       </c>
       <c r="K89">
         <v>1</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="B90">
         <v>6</v>
       </c>
       <c r="C90">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4808,27 +4860,18 @@
         <v>10</v>
       </c>
       <c r="I90" t="s">
-        <v>57</v>
-      </c>
-      <c r="J90" t="s">
-        <v>143</v>
-      </c>
-      <c r="K90">
-        <v>3</v>
-      </c>
-      <c r="L90" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="B91">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -4846,10 +4889,10 @@
         <v>10</v>
       </c>
       <c r="I91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J91" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="K91">
         <v>3</v>
@@ -4860,7 +4903,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B92">
         <v>6</v>
@@ -4884,10 +4927,10 @@
         <v>10</v>
       </c>
       <c r="I92" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J92" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="K92">
         <v>1</v>
@@ -4898,7 +4941,7 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B93">
         <v>6</v>
@@ -4925,18 +4968,18 @@
         <v>57</v>
       </c>
       <c r="J93" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="K93">
         <v>1</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B94">
         <v>6</v>
@@ -4960,27 +5003,27 @@
         <v>10</v>
       </c>
       <c r="I94" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J94" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K94">
         <v>3</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="B95">
         <v>6</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -5001,24 +5044,24 @@
         <v>57</v>
       </c>
       <c r="J95" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="K95">
         <v>1</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="B96">
         <v>6</v>
       </c>
       <c r="C96">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -5038,25 +5081,16 @@
       <c r="I96" t="s">
         <v>109</v>
       </c>
-      <c r="J96" t="s">
-        <v>182</v>
-      </c>
-      <c r="K96">
-        <v>1</v>
-      </c>
-      <c r="L96" s="8" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5077,24 +5111,24 @@
         <v>57</v>
       </c>
       <c r="J97" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="K97">
         <v>3</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
       <c r="C98">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5115,18 +5149,18 @@
         <v>58</v>
       </c>
       <c r="J98" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B99">
         <v>6</v>
@@ -5150,21 +5184,21 @@
         <v>10</v>
       </c>
       <c r="I99" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="J99" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="K99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="B100">
         <v>6</v>
@@ -5188,13 +5222,13 @@
         <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J100" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>106</v>
@@ -5202,7 +5236,7 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B101">
         <v>6</v>
@@ -5226,27 +5260,27 @@
         <v>10</v>
       </c>
       <c r="I101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J101" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5264,21 +5298,21 @@
         <v>10</v>
       </c>
       <c r="I102" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J102" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="K102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="B103">
         <v>6</v>
@@ -5305,18 +5339,18 @@
         <v>57</v>
       </c>
       <c r="J103" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="K103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -5343,24 +5377,24 @@
         <v>58</v>
       </c>
       <c r="J104" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="K104">
         <v>3</v>
       </c>
       <c r="L104" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B105">
         <v>6</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5381,10 +5415,10 @@
         <v>58</v>
       </c>
       <c r="J105" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="K105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>106</v>
@@ -5392,13 +5426,13 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>205</v>
+        <v>24</v>
       </c>
       <c r="B106">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5416,10 +5450,10 @@
         <v>10</v>
       </c>
       <c r="I106" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="J106" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="K106">
         <v>3</v>
@@ -5430,13 +5464,13 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>202</v>
+        <v>23</v>
       </c>
       <c r="B107">
         <v>6</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5457,7 +5491,7 @@
         <v>57</v>
       </c>
       <c r="J107" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="K107">
         <v>3</v>
@@ -5468,7 +5502,7 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="B108">
         <v>6</v>
@@ -5495,18 +5529,18 @@
         <v>57</v>
       </c>
       <c r="J108" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="K108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
       <c r="B109">
         <v>6</v>
@@ -5530,10 +5564,10 @@
         <v>10</v>
       </c>
       <c r="I109" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J109" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="K109">
         <v>3</v>
@@ -5544,7 +5578,7 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="B110">
         <v>6</v>
@@ -5568,10 +5602,10 @@
         <v>10</v>
       </c>
       <c r="I110" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J110" t="s">
-        <v>101</v>
+        <v>226</v>
       </c>
       <c r="K110">
         <v>3</v>
@@ -5582,7 +5616,7 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="B111">
         <v>6</v>
@@ -5606,27 +5640,27 @@
         <v>10</v>
       </c>
       <c r="I111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J111" t="s">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="K111">
         <v>3</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="B112">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -5647,18 +5681,18 @@
         <v>58</v>
       </c>
       <c r="J112" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="K112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="B113">
         <v>6</v>
@@ -5685,10 +5719,10 @@
         <v>57</v>
       </c>
       <c r="J113" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="K113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>106</v>
@@ -5696,13 +5730,13 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="B114">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -5720,27 +5754,27 @@
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J114" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="K114">
         <v>3</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B115">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -5761,24 +5795,24 @@
         <v>57</v>
       </c>
       <c r="J115" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>176</v>
+        <v>34</v>
       </c>
       <c r="B116">
         <v>6</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -5796,21 +5830,21 @@
         <v>10</v>
       </c>
       <c r="I116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J116" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="K116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L116" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="B117">
         <v>6</v>
@@ -5837,18 +5871,18 @@
         <v>109</v>
       </c>
       <c r="J117" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K117">
         <v>3</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>224</v>
+        <v>54</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -5872,27 +5906,27 @@
         <v>10</v>
       </c>
       <c r="I118" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J118" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="K118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="B119">
         <v>6</v>
       </c>
       <c r="C119">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -5910,21 +5944,21 @@
         <v>10</v>
       </c>
       <c r="I119" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J119" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L119" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B120">
         <v>6</v>
@@ -5951,10 +5985,10 @@
         <v>57</v>
       </c>
       <c r="J120" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="K120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>106</v>
@@ -5962,7 +5996,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B121">
         <v>6</v>
@@ -5989,46 +6023,397 @@
         <v>58</v>
       </c>
       <c r="J121" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="K121">
         <v>3</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="B122">
         <v>6</v>
       </c>
       <c r="C122">
+        <v>4</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122">
+        <v>90</v>
+      </c>
+      <c r="F122">
+        <v>10</v>
+      </c>
+      <c r="G122">
+        <v>10</v>
+      </c>
+      <c r="H122">
+        <v>10</v>
+      </c>
+      <c r="I122" t="s">
+        <v>57</v>
+      </c>
+      <c r="J122" t="s">
+        <v>175</v>
+      </c>
+      <c r="K122">
         <v>1</v>
       </c>
-      <c r="D122">
-        <v>2</v>
-      </c>
-      <c r="E122">
-        <v>90</v>
-      </c>
-      <c r="F122">
-        <v>10</v>
-      </c>
-      <c r="G122">
-        <v>10</v>
-      </c>
-      <c r="H122">
-        <v>10</v>
-      </c>
-      <c r="I122" t="s">
+      <c r="L122" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" t="s">
+        <v>174</v>
+      </c>
+      <c r="B123">
+        <v>6</v>
+      </c>
+      <c r="C123">
+        <v>3</v>
+      </c>
+      <c r="D123">
+        <v>2</v>
+      </c>
+      <c r="E123">
+        <v>90</v>
+      </c>
+      <c r="F123">
+        <v>10</v>
+      </c>
+      <c r="G123">
+        <v>10</v>
+      </c>
+      <c r="H123">
+        <v>10</v>
+      </c>
+      <c r="I123" t="s">
+        <v>57</v>
+      </c>
+      <c r="J123" t="s">
+        <v>175</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" t="s">
+        <v>155</v>
+      </c>
+      <c r="B124">
+        <v>6</v>
+      </c>
+      <c r="C124">
+        <v>6</v>
+      </c>
+      <c r="D124">
+        <v>2</v>
+      </c>
+      <c r="E124">
+        <v>90</v>
+      </c>
+      <c r="F124">
+        <v>10</v>
+      </c>
+      <c r="G124">
+        <v>10</v>
+      </c>
+      <c r="H124">
+        <v>10</v>
+      </c>
+      <c r="I124" t="s">
         <v>109</v>
       </c>
+      <c r="J124" t="s">
+        <v>102</v>
+      </c>
+      <c r="K124">
+        <v>3</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" t="s">
+        <v>222</v>
+      </c>
+      <c r="B125">
+        <v>6</v>
+      </c>
+      <c r="C125">
+        <v>6</v>
+      </c>
+      <c r="D125">
+        <v>2</v>
+      </c>
+      <c r="E125">
+        <v>90</v>
+      </c>
+      <c r="F125">
+        <v>10</v>
+      </c>
+      <c r="G125">
+        <v>10</v>
+      </c>
+      <c r="H125">
+        <v>10</v>
+      </c>
+      <c r="I125" t="s">
+        <v>109</v>
+      </c>
+      <c r="J125" t="s">
+        <v>102</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" t="s">
+        <v>36</v>
+      </c>
+      <c r="B126">
+        <v>6</v>
+      </c>
+      <c r="C126">
+        <v>4</v>
+      </c>
+      <c r="D126">
+        <v>2</v>
+      </c>
+      <c r="E126">
+        <v>90</v>
+      </c>
+      <c r="F126">
+        <v>10</v>
+      </c>
+      <c r="G126">
+        <v>10</v>
+      </c>
+      <c r="H126">
+        <v>10</v>
+      </c>
+      <c r="I126" t="s">
+        <v>57</v>
+      </c>
+      <c r="J126" t="s">
+        <v>131</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127">
+        <v>6</v>
+      </c>
+      <c r="C127">
+        <v>4</v>
+      </c>
+      <c r="D127">
+        <v>2</v>
+      </c>
+      <c r="E127">
+        <v>90</v>
+      </c>
+      <c r="F127">
+        <v>10</v>
+      </c>
+      <c r="G127">
+        <v>10</v>
+      </c>
+      <c r="H127">
+        <v>10</v>
+      </c>
+      <c r="I127" t="s">
+        <v>58</v>
+      </c>
+      <c r="J127" t="s">
+        <v>232</v>
+      </c>
+      <c r="K127">
+        <v>3</v>
+      </c>
+      <c r="L127" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" t="s">
+        <v>37</v>
+      </c>
+      <c r="B128">
+        <v>6</v>
+      </c>
+      <c r="C128">
+        <v>6</v>
+      </c>
+      <c r="D128">
+        <v>2</v>
+      </c>
+      <c r="E128">
+        <v>90</v>
+      </c>
+      <c r="F128">
+        <v>10</v>
+      </c>
+      <c r="G128">
+        <v>10</v>
+      </c>
+      <c r="H128">
+        <v>10</v>
+      </c>
+      <c r="I128" t="s">
+        <v>57</v>
+      </c>
+      <c r="J128" t="s">
+        <v>156</v>
+      </c>
+      <c r="K128">
+        <v>3</v>
+      </c>
+      <c r="L128" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129">
+        <v>6</v>
+      </c>
+      <c r="C129">
+        <v>6</v>
+      </c>
+      <c r="D129">
+        <v>2</v>
+      </c>
+      <c r="E129">
+        <v>90</v>
+      </c>
+      <c r="F129">
+        <v>10</v>
+      </c>
+      <c r="G129">
+        <v>10</v>
+      </c>
+      <c r="H129">
+        <v>10</v>
+      </c>
+      <c r="I129" t="s">
+        <v>58</v>
+      </c>
+      <c r="J129" t="s">
+        <v>238</v>
+      </c>
+      <c r="K129">
+        <v>3</v>
+      </c>
+      <c r="L129" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>251</v>
+      </c>
+      <c r="B130">
+        <v>6</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+      <c r="E130">
+        <v>90</v>
+      </c>
+      <c r="F130">
+        <v>7</v>
+      </c>
+      <c r="G130">
+        <v>7</v>
+      </c>
+      <c r="H130">
+        <v>10</v>
+      </c>
+      <c r="I130" t="s">
+        <v>109</v>
+      </c>
+      <c r="J130" t="s">
+        <v>252</v>
+      </c>
+      <c r="K130">
+        <v>3</v>
+      </c>
+      <c r="L130" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>223</v>
+      </c>
+      <c r="B131">
+        <v>6</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+      <c r="E131">
+        <v>90</v>
+      </c>
+      <c r="F131">
+        <v>10</v>
+      </c>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>10</v>
+      </c>
+      <c r="I131" t="s">
+        <v>109</v>
+      </c>
+      <c r="J131" t="s">
+        <v>253</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131" s="8" t="s">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L260" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:L269" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
@@ -6040,20 +6425,20 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I269:I296" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I279:I306" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
       <formula1>"elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L302:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L312:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
       <formula1>"蓝色,绿色,灰色,红色,金色"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E1048576" xr:uid="{067929F4-68AD-4FCF-9645-B8AA87BCECB2}">
       <formula1>0</formula1>
       <formula2>90</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L301" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L311" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
       <formula1>"blue,green,grey,red,yellow"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I268" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I278" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
       <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">

--- a/Source/arkD - 副本.xlsx
+++ b/Source/arkD - 副本.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37b141e1e60375e0/Arknights/ArknightsIDcard-Ebranch/ArknightsIDCard/Source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OneDrive\Arknights\ArknightsIDcard-Ebranch\ArknightsIDCard\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{CEBBFEC2-EB42-4FE1-B0B7-F54EA67B262D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3367B928-201D-4293-950E-6EA74EB6B706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="14620" windowHeight="25220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="11596" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="其他信息" sheetId="2" r:id="rId1"/>
     <sheet name="练度表" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$143</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="269">
   <si>
     <t>陈</t>
   </si>
@@ -866,9 +866,6 @@
     <t>PUS-Y</t>
   </si>
   <si>
-    <t>2025.05.02</t>
-  </si>
-  <si>
     <t>BEA-Y</t>
   </si>
   <si>
@@ -909,6 +906,54 @@
   </si>
   <si>
     <t>ALC-X</t>
+  </si>
+  <si>
+    <t>2025.08.09</t>
+  </si>
+  <si>
+    <t>司霆惊蛰</t>
+  </si>
+  <si>
+    <t>PRO-X</t>
+  </si>
+  <si>
+    <t>斩业星熊</t>
+  </si>
+  <si>
+    <t>RPR-Y</t>
+  </si>
+  <si>
+    <t>FUN-Y</t>
+  </si>
+  <si>
+    <t>CCR-Y</t>
+  </si>
+  <si>
+    <t>SPC-X</t>
+  </si>
+  <si>
+    <t>PRI-X</t>
+  </si>
+  <si>
+    <t>SOC-X</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>SO-A</t>
+  </si>
+  <si>
+    <t>酒神</t>
+  </si>
+  <si>
+    <t>遥</t>
+  </si>
+  <si>
+    <t>BLS-Y</t>
+  </si>
+  <si>
+    <t>EXE-Y</t>
   </si>
 </sst>
 </file>
@@ -1334,11 +1379,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6345695-2B66-457B-8BCC-599D10A5115F}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.4609375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.4609375" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.84375" style="2"/>
+    <col min="1" max="1" width="20.46484375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.46484375" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.86328125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1376,7 +1421,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1490,15 +1535,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L131"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <dimension ref="A1:L143"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.15234375" customWidth="1"/>
-    <col min="9" max="9" width="10.3828125" customWidth="1"/>
-    <col min="12" max="12" width="8.84375" style="8"/>
+    <col min="1" max="1" width="19.1328125" customWidth="1"/>
+    <col min="9" max="9" width="10.3984375" customWidth="1"/>
+    <col min="12" max="12" width="8.86328125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="13" customFormat="1" ht="37.299999999999997" customHeight="1">
+    <row r="1" spans="1:12" s="13" customFormat="1" ht="37.35" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>49</v>
       </c>
@@ -1564,7 +1609,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="32.5" customHeight="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="32.549999999999997" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>110</v>
       </c>
@@ -1666,7 +1711,7 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J5" t="s">
         <v>81</v>
@@ -1783,7 +1828,7 @@
         <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K8">
         <v>3</v>
@@ -1970,10 +2015,10 @@
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K13">
         <v>3</v>
@@ -2098,7 +2143,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2353,7 +2398,7 @@
         <v>58</v>
       </c>
       <c r="J23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -2440,13 +2485,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2464,27 +2509,27 @@
         <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J26" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>154</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2505,7 +2550,7 @@
         <v>58</v>
       </c>
       <c r="J27" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2516,13 +2561,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -2540,27 +2585,27 @@
         <v>10</v>
       </c>
       <c r="I28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J28" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2578,21 +2623,21 @@
         <v>10</v>
       </c>
       <c r="I29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J29" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -2616,10 +2661,10 @@
         <v>10</v>
       </c>
       <c r="I30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>229</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -2654,27 +2699,27 @@
         <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J31" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2692,27 +2737,27 @@
         <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J32" t="s">
-        <v>229</v>
+        <v>104</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2730,21 +2775,21 @@
         <v>10</v>
       </c>
       <c r="I33" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J33" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -2771,24 +2816,24 @@
         <v>109</v>
       </c>
       <c r="J34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K34">
         <v>3</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -2809,7 +2854,7 @@
         <v>57</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -2820,13 +2865,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2844,13 +2889,13 @@
         <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J36" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>107</v>
@@ -2858,7 +2903,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -2882,10 +2927,10 @@
         <v>10</v>
       </c>
       <c r="I37" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J37" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -2896,13 +2941,13 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2920,27 +2965,27 @@
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="K38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>195</v>
+        <v>9</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2958,21 +3003,21 @@
         <v>10</v>
       </c>
       <c r="I39" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="J39" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -2996,27 +3041,27 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J40" t="s">
-        <v>186</v>
+        <v>85</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -3037,24 +3082,24 @@
         <v>57</v>
       </c>
       <c r="J41" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -3072,27 +3117,27 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J42" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K42">
         <v>3</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>179</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3110,27 +3155,27 @@
         <v>10</v>
       </c>
       <c r="I43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J43" t="s">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="K43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -3148,27 +3193,27 @@
         <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K44">
         <v>3</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -3186,21 +3231,21 @@
         <v>10</v>
       </c>
       <c r="I45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J45" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B46">
         <v>6</v>
@@ -3224,21 +3269,21 @@
         <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="J46" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B47">
         <v>6</v>
@@ -3265,10 +3310,10 @@
         <v>57</v>
       </c>
       <c r="J47" t="s">
-        <v>234</v>
+        <v>86</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>107</v>
@@ -3276,13 +3321,13 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>67</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -3300,21 +3345,21 @@
         <v>10</v>
       </c>
       <c r="I48" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J48" t="s">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -3341,24 +3386,24 @@
         <v>57</v>
       </c>
       <c r="J49" t="s">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -3379,18 +3424,18 @@
         <v>57</v>
       </c>
       <c r="J50" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="B51">
         <v>6</v>
@@ -3405,65 +3450,74 @@
         <v>90</v>
       </c>
       <c r="F51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I51" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J51" t="s">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>235</v>
+        <v>69</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52">
+        <v>6</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>90</v>
+      </c>
+      <c r="F52">
+        <v>10</v>
+      </c>
+      <c r="G52">
+        <v>10</v>
+      </c>
+      <c r="H52">
+        <v>10</v>
+      </c>
+      <c r="I52" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52">
         <v>1</v>
       </c>
-      <c r="D52">
-        <v>2</v>
-      </c>
-      <c r="E52">
-        <v>90</v>
-      </c>
-      <c r="F52">
-        <v>10</v>
-      </c>
-      <c r="G52">
-        <v>10</v>
-      </c>
-      <c r="H52">
-        <v>10</v>
-      </c>
-      <c r="I52" t="s">
-        <v>109</v>
+      <c r="L52" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -3484,18 +3538,18 @@
         <v>58</v>
       </c>
       <c r="J53" t="s">
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>244</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -3519,27 +3573,27 @@
         <v>10</v>
       </c>
       <c r="I54" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J54" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>235</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3557,27 +3611,18 @@
         <v>10</v>
       </c>
       <c r="I55" t="s">
-        <v>58</v>
-      </c>
-      <c r="J55" t="s">
-        <v>133</v>
-      </c>
-      <c r="K55">
-        <v>3</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B56">
         <v>6</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -3595,27 +3640,18 @@
         <v>10</v>
       </c>
       <c r="I56" t="s">
-        <v>57</v>
-      </c>
-      <c r="J56" t="s">
-        <v>133</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3633,10 +3669,10 @@
         <v>10</v>
       </c>
       <c r="I57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J57" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -3647,13 +3683,13 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="B58">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -3674,24 +3710,24 @@
         <v>57</v>
       </c>
       <c r="J58" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="K58">
         <v>3</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -3709,10 +3745,10 @@
         <v>10</v>
       </c>
       <c r="I59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J59" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K59">
         <v>3</v>
@@ -3723,13 +3759,13 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>245</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3750,10 +3786,10 @@
         <v>58</v>
       </c>
       <c r="J60" t="s">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>105</v>
@@ -3761,13 +3797,13 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -3788,24 +3824,24 @@
         <v>57</v>
       </c>
       <c r="J61" t="s">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="K61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>247</v>
+        <v>71</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3814,22 +3850,22 @@
         <v>90</v>
       </c>
       <c r="F62">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G62">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H62">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I62" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J62" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>105</v>
@@ -3837,13 +3873,13 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="B63">
         <v>6</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -3861,27 +3897,27 @@
         <v>10</v>
       </c>
       <c r="I63" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J63" t="s">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -3902,24 +3938,24 @@
         <v>57</v>
       </c>
       <c r="J64" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>13</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3937,18 +3973,27 @@
         <v>10</v>
       </c>
       <c r="I65" t="s">
-        <v>109</v>
+        <v>58</v>
+      </c>
+      <c r="J65" t="s">
+        <v>232</v>
+      </c>
+      <c r="K65">
+        <v>3</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3966,27 +4011,27 @@
         <v>10</v>
       </c>
       <c r="I66" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J66" t="s">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="B67">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -4004,10 +4049,10 @@
         <v>10</v>
       </c>
       <c r="I67" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J67" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="K67">
         <v>3</v>
@@ -4018,13 +4063,13 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -4042,10 +4087,10 @@
         <v>10</v>
       </c>
       <c r="I68" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J68" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -4056,13 +4101,13 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="B69">
         <v>6</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -4083,18 +4128,18 @@
         <v>57</v>
       </c>
       <c r="J69" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>218</v>
       </c>
       <c r="B70">
         <v>6</v>
@@ -4118,27 +4163,18 @@
         <v>10</v>
       </c>
       <c r="I70" t="s">
-        <v>57</v>
-      </c>
-      <c r="J70" t="s">
-        <v>91</v>
-      </c>
-      <c r="K70">
-        <v>2</v>
-      </c>
-      <c r="L70" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4156,13 +4192,13 @@
         <v>10</v>
       </c>
       <c r="I71" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="J71" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="K71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>105</v>
@@ -4170,13 +4206,13 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="B72">
         <v>6</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -4194,10 +4230,10 @@
         <v>10</v>
       </c>
       <c r="I72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J72" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="K72">
         <v>3</v>
@@ -4208,13 +4244,13 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="B73">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -4232,13 +4268,13 @@
         <v>10</v>
       </c>
       <c r="I73" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J73" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="K73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>105</v>
@@ -4246,13 +4282,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -4273,10 +4309,10 @@
         <v>57</v>
       </c>
       <c r="J74" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="K74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>105</v>
@@ -4284,13 +4320,13 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>219</v>
+        <v>72</v>
       </c>
       <c r="B75">
         <v>6</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -4308,13 +4344,13 @@
         <v>10</v>
       </c>
       <c r="I75" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J75" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>105</v>
@@ -4322,13 +4358,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="B76">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4349,10 +4385,10 @@
         <v>57</v>
       </c>
       <c r="J76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>105</v>
@@ -4360,7 +4396,7 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77">
         <v>6</v>
@@ -4384,21 +4420,21 @@
         <v>10</v>
       </c>
       <c r="I77" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J77" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -4422,10 +4458,10 @@
         <v>10</v>
       </c>
       <c r="I78" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J78" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="K78">
         <v>3</v>
@@ -4436,13 +4472,13 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="B79">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4460,21 +4496,21 @@
         <v>10</v>
       </c>
       <c r="I79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J79" t="s">
-        <v>159</v>
+        <v>258</v>
       </c>
       <c r="K79">
         <v>3</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="B80">
         <v>6</v>
@@ -4501,10 +4537,10 @@
         <v>57</v>
       </c>
       <c r="J80" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>105</v>
@@ -4512,13 +4548,13 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B81">
         <v>6</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -4536,21 +4572,21 @@
         <v>10</v>
       </c>
       <c r="I81" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J81" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="B82">
         <v>6</v>
@@ -4574,27 +4610,27 @@
         <v>10</v>
       </c>
       <c r="I82" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J82" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="K82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="B83">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -4614,45 +4650,63 @@
       <c r="I83" t="s">
         <v>57</v>
       </c>
+      <c r="J83" t="s">
+        <v>259</v>
+      </c>
+      <c r="K83">
+        <v>3</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="B84">
         <v>6</v>
       </c>
       <c r="C84">
+        <v>6</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>90</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84">
+        <v>10</v>
+      </c>
+      <c r="H84">
+        <v>10</v>
+      </c>
+      <c r="I84" t="s">
+        <v>58</v>
+      </c>
+      <c r="J84" t="s">
+        <v>159</v>
+      </c>
+      <c r="K84">
         <v>1</v>
       </c>
-      <c r="D84">
-        <v>2</v>
-      </c>
-      <c r="E84">
-        <v>90</v>
-      </c>
-      <c r="F84">
-        <v>10</v>
-      </c>
-      <c r="G84">
-        <v>10</v>
-      </c>
-      <c r="H84">
-        <v>10</v>
-      </c>
-      <c r="I84" t="s">
-        <v>109</v>
+      <c r="L84" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B85">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4670,13 +4724,13 @@
         <v>10</v>
       </c>
       <c r="I85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J85" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>105</v>
@@ -4684,13 +4738,13 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="B86">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -4708,21 +4762,21 @@
         <v>10</v>
       </c>
       <c r="I86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J86" t="s">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="K86">
         <v>3</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>207</v>
       </c>
       <c r="B87">
         <v>6</v>
@@ -4749,7 +4803,7 @@
         <v>57</v>
       </c>
       <c r="J87" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="K87">
         <v>3</v>
@@ -4760,13 +4814,13 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>220</v>
       </c>
       <c r="B88">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -4784,27 +4838,27 @@
         <v>10</v>
       </c>
       <c r="I88" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J88" t="s">
-        <v>236</v>
+        <v>93</v>
       </c>
       <c r="K88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B89">
         <v>6</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4822,13 +4876,13 @@
         <v>10</v>
       </c>
       <c r="I89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J89" t="s">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>105</v>
@@ -4836,13 +4890,13 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>237</v>
+        <v>29</v>
       </c>
       <c r="B90">
         <v>6</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4860,12 +4914,21 @@
         <v>10</v>
       </c>
       <c r="I90" t="s">
-        <v>109</v>
+        <v>57</v>
+      </c>
+      <c r="J90" t="s">
+        <v>93</v>
+      </c>
+      <c r="K90">
+        <v>3</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="B91">
         <v>6</v>
@@ -4892,24 +4955,24 @@
         <v>57</v>
       </c>
       <c r="J91" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="K91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="B92">
         <v>6</v>
       </c>
       <c r="C92">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4927,27 +4990,27 @@
         <v>10</v>
       </c>
       <c r="I92" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J92" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B93">
         <v>6</v>
       </c>
       <c r="C93">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -4968,24 +5031,24 @@
         <v>57</v>
       </c>
       <c r="J93" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="K93">
         <v>1</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B94">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -5012,12 +5075,12 @@
         <v>3</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B95">
         <v>6</v>
@@ -5044,24 +5107,24 @@
         <v>57</v>
       </c>
       <c r="J95" t="s">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>250</v>
+        <v>31</v>
       </c>
       <c r="B96">
         <v>6</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -5079,18 +5142,27 @@
         <v>10</v>
       </c>
       <c r="I96" t="s">
-        <v>109</v>
+        <v>58</v>
+      </c>
+      <c r="J96" t="s">
+        <v>236</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5111,24 +5183,24 @@
         <v>57</v>
       </c>
       <c r="J97" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="K97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5146,27 +5218,27 @@
         <v>10</v>
       </c>
       <c r="I98" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J98" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="K98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="B99">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5184,13 +5256,13 @@
         <v>10</v>
       </c>
       <c r="I99" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J99" t="s">
-        <v>96</v>
+        <v>227</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>107</v>
@@ -5198,7 +5270,7 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B100">
         <v>6</v>
@@ -5222,21 +5294,21 @@
         <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J100" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B101">
         <v>6</v>
@@ -5260,13 +5332,13 @@
         <v>10</v>
       </c>
       <c r="I101" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J101" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="K101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>107</v>
@@ -5274,13 +5346,13 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5298,21 +5370,21 @@
         <v>10</v>
       </c>
       <c r="I102" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J102" t="s">
-        <v>169</v>
+        <v>232</v>
       </c>
       <c r="K102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="B103">
         <v>6</v>
@@ -5339,24 +5411,24 @@
         <v>57</v>
       </c>
       <c r="J103" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="K103">
         <v>1</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="B104">
         <v>6</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5374,21 +5446,12 @@
         <v>10</v>
       </c>
       <c r="I104" t="s">
-        <v>58</v>
-      </c>
-      <c r="J104" t="s">
-        <v>99</v>
-      </c>
-      <c r="K104">
-        <v>3</v>
-      </c>
-      <c r="L104" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B105">
         <v>6</v>
@@ -5412,27 +5475,27 @@
         <v>10</v>
       </c>
       <c r="I105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J105" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="K105">
         <v>3</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="B106">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5450,27 +5513,27 @@
         <v>10</v>
       </c>
       <c r="I106" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="J106" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K106">
         <v>3</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B107">
         <v>6</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5488,21 +5551,21 @@
         <v>10</v>
       </c>
       <c r="I107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J107" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="K107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B108">
         <v>6</v>
@@ -5529,7 +5592,7 @@
         <v>57</v>
       </c>
       <c r="J108" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K108">
         <v>1</v>
@@ -5540,7 +5603,7 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>208</v>
+        <v>22</v>
       </c>
       <c r="B109">
         <v>6</v>
@@ -5564,27 +5627,27 @@
         <v>10</v>
       </c>
       <c r="I109" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J109" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="K109">
         <v>3</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="B110">
         <v>6</v>
       </c>
       <c r="C110">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -5602,21 +5665,21 @@
         <v>10</v>
       </c>
       <c r="I110" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J110" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="K110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="B111">
         <v>6</v>
@@ -5640,27 +5703,27 @@
         <v>10</v>
       </c>
       <c r="I111" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J111" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="K111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>263</v>
       </c>
       <c r="B112">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -5678,27 +5741,27 @@
         <v>10</v>
       </c>
       <c r="I112" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J112" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="K112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="B113">
         <v>6</v>
       </c>
       <c r="C113">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5716,27 +5779,27 @@
         <v>10</v>
       </c>
       <c r="I113" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J113" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="K113">
         <v>3</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="B114">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -5754,10 +5817,10 @@
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J114" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="K114">
         <v>3</v>
@@ -5768,7 +5831,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="B115">
         <v>6</v>
@@ -5792,21 +5855,21 @@
         <v>10</v>
       </c>
       <c r="I115" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J115" t="s">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="K115">
         <v>3</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B116">
         <v>6</v>
@@ -5830,27 +5893,27 @@
         <v>10</v>
       </c>
       <c r="I116" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J116" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B117">
         <v>6</v>
       </c>
       <c r="C117">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -5868,21 +5931,21 @@
         <v>10</v>
       </c>
       <c r="I117" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J117" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="K117">
         <v>3</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -5909,18 +5972,18 @@
         <v>57</v>
       </c>
       <c r="J118" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="K118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="B119">
         <v>6</v>
@@ -5944,10 +6007,10 @@
         <v>10</v>
       </c>
       <c r="I119" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J119" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="K119">
         <v>3</v>
@@ -5958,7 +6021,7 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="B120">
         <v>6</v>
@@ -5985,24 +6048,24 @@
         <v>57</v>
       </c>
       <c r="J120" t="s">
-        <v>102</v>
+        <v>226</v>
       </c>
       <c r="K120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>35</v>
+        <v>266</v>
       </c>
       <c r="B121">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -6020,27 +6083,27 @@
         <v>10</v>
       </c>
       <c r="I121" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J121" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="K121">
         <v>3</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="B122">
         <v>6</v>
       </c>
       <c r="C122">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6058,27 +6121,27 @@
         <v>10</v>
       </c>
       <c r="I122" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J122" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="K122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L122" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>174</v>
+        <v>33</v>
       </c>
       <c r="B123">
         <v>6</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -6096,10 +6159,10 @@
         <v>10</v>
       </c>
       <c r="I123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J123" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K123">
         <v>1</v>
@@ -6110,7 +6173,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="B124">
         <v>6</v>
@@ -6134,10 +6197,10 @@
         <v>10</v>
       </c>
       <c r="I124" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J124" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="K124">
         <v>3</v>
@@ -6148,13 +6211,13 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B125">
         <v>6</v>
       </c>
       <c r="C125">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -6172,13 +6235,13 @@
         <v>10</v>
       </c>
       <c r="I125" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J125" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="K125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>106</v>
@@ -6186,13 +6249,13 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="B126">
         <v>6</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -6213,24 +6276,24 @@
         <v>57</v>
       </c>
       <c r="J126" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="K126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L126" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B127">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -6251,18 +6314,18 @@
         <v>58</v>
       </c>
       <c r="J127" t="s">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="K127">
         <v>3</v>
       </c>
       <c r="L127" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -6286,21 +6349,21 @@
         <v>10</v>
       </c>
       <c r="I128" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J128" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="K128">
         <v>3</v>
       </c>
       <c r="L128" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B129">
         <v>6</v>
@@ -6324,27 +6387,27 @@
         <v>10</v>
       </c>
       <c r="I129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J129" t="s">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="K129">
         <v>3</v>
       </c>
       <c r="L129" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="B130">
         <v>6</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -6353,67 +6416,523 @@
         <v>90</v>
       </c>
       <c r="F130">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G130">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H130">
         <v>10</v>
       </c>
       <c r="I130" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J130" t="s">
-        <v>252</v>
+        <v>103</v>
       </c>
       <c r="K130">
         <v>3</v>
       </c>
       <c r="L130" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="B131">
         <v>6</v>
       </c>
       <c r="C131">
+        <v>6</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+      <c r="E131">
+        <v>90</v>
+      </c>
+      <c r="F131">
+        <v>10</v>
+      </c>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>10</v>
+      </c>
+      <c r="I131" t="s">
+        <v>57</v>
+      </c>
+      <c r="J131" t="s">
+        <v>102</v>
+      </c>
+      <c r="K131">
         <v>1</v>
-      </c>
-      <c r="D131">
-        <v>2</v>
-      </c>
-      <c r="E131">
-        <v>90</v>
-      </c>
-      <c r="F131">
-        <v>10</v>
-      </c>
-      <c r="G131">
-        <v>10</v>
-      </c>
-      <c r="H131">
-        <v>10</v>
-      </c>
-      <c r="I131" t="s">
-        <v>109</v>
-      </c>
-      <c r="J131" t="s">
-        <v>253</v>
-      </c>
-      <c r="K131">
-        <v>2</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>106</v>
       </c>
     </row>
+    <row r="132" spans="1:12">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132">
+        <v>6</v>
+      </c>
+      <c r="C132">
+        <v>6</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+      <c r="E132">
+        <v>90</v>
+      </c>
+      <c r="F132">
+        <v>10</v>
+      </c>
+      <c r="G132">
+        <v>10</v>
+      </c>
+      <c r="H132">
+        <v>10</v>
+      </c>
+      <c r="I132" t="s">
+        <v>58</v>
+      </c>
+      <c r="J132" t="s">
+        <v>232</v>
+      </c>
+      <c r="K132">
+        <v>3</v>
+      </c>
+      <c r="L132" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" t="s">
+        <v>79</v>
+      </c>
+      <c r="B133">
+        <v>6</v>
+      </c>
+      <c r="C133">
+        <v>4</v>
+      </c>
+      <c r="D133">
+        <v>2</v>
+      </c>
+      <c r="E133">
+        <v>90</v>
+      </c>
+      <c r="F133">
+        <v>10</v>
+      </c>
+      <c r="G133">
+        <v>10</v>
+      </c>
+      <c r="H133">
+        <v>10</v>
+      </c>
+      <c r="I133" t="s">
+        <v>57</v>
+      </c>
+      <c r="J133" t="s">
+        <v>175</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" t="s">
+        <v>174</v>
+      </c>
+      <c r="B134">
+        <v>6</v>
+      </c>
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134">
+        <v>90</v>
+      </c>
+      <c r="F134">
+        <v>10</v>
+      </c>
+      <c r="G134">
+        <v>10</v>
+      </c>
+      <c r="H134">
+        <v>10</v>
+      </c>
+      <c r="I134" t="s">
+        <v>57</v>
+      </c>
+      <c r="J134" t="s">
+        <v>175</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" t="s">
+        <v>155</v>
+      </c>
+      <c r="B135">
+        <v>6</v>
+      </c>
+      <c r="C135">
+        <v>6</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+      <c r="E135">
+        <v>90</v>
+      </c>
+      <c r="F135">
+        <v>10</v>
+      </c>
+      <c r="G135">
+        <v>10</v>
+      </c>
+      <c r="H135">
+        <v>10</v>
+      </c>
+      <c r="I135" t="s">
+        <v>109</v>
+      </c>
+      <c r="J135" t="s">
+        <v>102</v>
+      </c>
+      <c r="K135">
+        <v>3</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" t="s">
+        <v>222</v>
+      </c>
+      <c r="B136">
+        <v>6</v>
+      </c>
+      <c r="C136">
+        <v>6</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+      <c r="E136">
+        <v>90</v>
+      </c>
+      <c r="F136">
+        <v>10</v>
+      </c>
+      <c r="G136">
+        <v>10</v>
+      </c>
+      <c r="H136">
+        <v>10</v>
+      </c>
+      <c r="I136" t="s">
+        <v>109</v>
+      </c>
+      <c r="J136" t="s">
+        <v>102</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B137">
+        <v>6</v>
+      </c>
+      <c r="C137">
+        <v>6</v>
+      </c>
+      <c r="D137">
+        <v>2</v>
+      </c>
+      <c r="E137">
+        <v>90</v>
+      </c>
+      <c r="F137">
+        <v>10</v>
+      </c>
+      <c r="G137">
+        <v>10</v>
+      </c>
+      <c r="H137">
+        <v>10</v>
+      </c>
+      <c r="I137" t="s">
+        <v>109</v>
+      </c>
+      <c r="J137" t="s">
+        <v>268</v>
+      </c>
+      <c r="K137">
+        <v>3</v>
+      </c>
+      <c r="L137" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138">
+        <v>6</v>
+      </c>
+      <c r="C138">
+        <v>4</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138">
+        <v>90</v>
+      </c>
+      <c r="F138">
+        <v>10</v>
+      </c>
+      <c r="G138">
+        <v>10</v>
+      </c>
+      <c r="H138">
+        <v>10</v>
+      </c>
+      <c r="I138" t="s">
+        <v>57</v>
+      </c>
+      <c r="J138" t="s">
+        <v>131</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" t="s">
+        <v>36</v>
+      </c>
+      <c r="B139">
+        <v>6</v>
+      </c>
+      <c r="C139">
+        <v>4</v>
+      </c>
+      <c r="D139">
+        <v>2</v>
+      </c>
+      <c r="E139">
+        <v>90</v>
+      </c>
+      <c r="F139">
+        <v>10</v>
+      </c>
+      <c r="G139">
+        <v>10</v>
+      </c>
+      <c r="H139">
+        <v>10</v>
+      </c>
+      <c r="I139" t="s">
+        <v>58</v>
+      </c>
+      <c r="J139" t="s">
+        <v>232</v>
+      </c>
+      <c r="K139">
+        <v>3</v>
+      </c>
+      <c r="L139" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140">
+        <v>6</v>
+      </c>
+      <c r="C140">
+        <v>6</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+      <c r="E140">
+        <v>90</v>
+      </c>
+      <c r="F140">
+        <v>10</v>
+      </c>
+      <c r="G140">
+        <v>10</v>
+      </c>
+      <c r="H140">
+        <v>10</v>
+      </c>
+      <c r="I140" t="s">
+        <v>57</v>
+      </c>
+      <c r="J140" t="s">
+        <v>156</v>
+      </c>
+      <c r="K140">
+        <v>3</v>
+      </c>
+      <c r="L140" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141">
+        <v>6</v>
+      </c>
+      <c r="C141">
+        <v>6</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+      <c r="E141">
+        <v>90</v>
+      </c>
+      <c r="F141">
+        <v>10</v>
+      </c>
+      <c r="G141">
+        <v>10</v>
+      </c>
+      <c r="H141">
+        <v>10</v>
+      </c>
+      <c r="I141" t="s">
+        <v>58</v>
+      </c>
+      <c r="J141" t="s">
+        <v>238</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" t="s">
+        <v>250</v>
+      </c>
+      <c r="B142">
+        <v>6</v>
+      </c>
+      <c r="C142">
+        <v>5</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+      <c r="E142">
+        <v>90</v>
+      </c>
+      <c r="F142">
+        <v>10</v>
+      </c>
+      <c r="G142">
+        <v>10</v>
+      </c>
+      <c r="H142">
+        <v>10</v>
+      </c>
+      <c r="I142" t="s">
+        <v>109</v>
+      </c>
+      <c r="J142" t="s">
+        <v>251</v>
+      </c>
+      <c r="K142">
+        <v>3</v>
+      </c>
+      <c r="L142" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" t="s">
+        <v>223</v>
+      </c>
+      <c r="B143">
+        <v>6</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143">
+        <v>90</v>
+      </c>
+      <c r="F143">
+        <v>10</v>
+      </c>
+      <c r="G143">
+        <v>10</v>
+      </c>
+      <c r="H143">
+        <v>10</v>
+      </c>
+      <c r="I143" t="s">
+        <v>57</v>
+      </c>
+      <c r="J143" t="s">
+        <v>252</v>
+      </c>
+      <c r="K143">
+        <v>3</v>
+      </c>
+      <c r="L143" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L269" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:L143" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
@@ -6425,25 +6944,18 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I279:I306" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I144:I171" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
       <formula1>"elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L312:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L177:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
       <formula1>"蓝色,绿色,灰色,红色,金色"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I143" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
+      <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E1048576" xr:uid="{067929F4-68AD-4FCF-9645-B8AA87BCECB2}">
       <formula1>0</formula1>
       <formula2>90</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L311" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
-      <formula1>"blue,green,grey,red,yellow"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I278" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
-      <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">
-      <formula1>1</formula1>
-      <formula2>3</formula2>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C1048576" xr:uid="{84D7772C-943A-4833-B43B-BB959E902FB7}">
       <formula1>1</formula1>
@@ -6457,6 +6969,13 @@
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L176" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
+      <formula1>"blue,green,grey,red,yellow"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">
+      <formula1>1</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Source/arkD - 副本.xlsx
+++ b/Source/arkD - 副本.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OneDrive\Arknights\ArknightsIDcard-Ebranch\ArknightsIDCard\Source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37b141e1e60375e0/Arknights/ArknightsIDcard-Ebranch/ArknightsIDCard/Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3367B928-201D-4293-950E-6EA74EB6B706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{F2DC7825-D08F-4350-8148-185F81D8CED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530F5960-FBFE-4DDC-B94B-028EAAFBB3A6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="11596" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="练度表" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$335</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="297">
   <si>
     <t>陈</t>
   </si>
@@ -519,441 +519,524 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>四五星三技能填0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不填则随机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白铁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOL-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOL-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伺夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斥罪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缄默德克萨斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUM-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焰影苇草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCR-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仇白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麒麟X夜刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUS-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊内丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLX-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRP-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缪尔赛思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霍尔海雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淬羽赫默</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOM-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UMD-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣约送葬人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提丰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琳琅诗怀雅</t>
+  </si>
+  <si>
+    <t>MER-X</t>
+  </si>
+  <si>
+    <t>CEN-X</t>
+  </si>
+  <si>
+    <t>REA-X</t>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉</t>
+  </si>
+  <si>
+    <t>涤火杰西卡</t>
+  </si>
+  <si>
+    <t>BLS-X</t>
+  </si>
+  <si>
+    <t>赫德雷</t>
+  </si>
+  <si>
+    <t>FOR-X</t>
+  </si>
+  <si>
+    <t>ARC-X</t>
+  </si>
+  <si>
+    <t>薇薇安娜</t>
+  </si>
+  <si>
+    <t>止颂</t>
+  </si>
+  <si>
+    <t>UNY-X</t>
+  </si>
+  <si>
+    <t>塑心</t>
+  </si>
+  <si>
+    <t>锏</t>
+  </si>
+  <si>
+    <t>FUN-X</t>
+  </si>
+  <si>
+    <t>INC-X</t>
+  </si>
+  <si>
+    <t>DEC-Y</t>
+  </si>
+  <si>
+    <t>莱伊</t>
+  </si>
+  <si>
+    <t>FGT-Y</t>
+  </si>
+  <si>
+    <t>FGT-X</t>
+  </si>
+  <si>
+    <t>左乐</t>
+  </si>
+  <si>
+    <t>黍</t>
+  </si>
+  <si>
+    <t>SBL-X</t>
+  </si>
+  <si>
+    <t>GUA-X</t>
+  </si>
+  <si>
+    <t>SPT-X</t>
+  </si>
+  <si>
+    <t>艾拉</t>
+  </si>
+  <si>
+    <t>TRP-Δ</t>
+  </si>
+  <si>
+    <t>TAC-X</t>
+  </si>
+  <si>
+    <t>阿斯卡纶</t>
+  </si>
+  <si>
+    <t>LOR-X</t>
+  </si>
+  <si>
+    <t>维什戴尔</t>
+  </si>
+  <si>
+    <t>BOM-X</t>
+  </si>
+  <si>
+    <t>逻各斯</t>
+  </si>
+  <si>
+    <t>魔王</t>
+  </si>
+  <si>
+    <t>CCR-X</t>
+  </si>
+  <si>
+    <t>CCR-Δ</t>
+  </si>
+  <si>
+    <t>乌尔比安</t>
+  </si>
+  <si>
+    <t>HUN-X</t>
+  </si>
+  <si>
+    <t>2019.05.06</t>
+  </si>
+  <si>
+    <t>妮芙</t>
+  </si>
+  <si>
+    <t>RPR-X</t>
+  </si>
+  <si>
+    <t>忍冬</t>
+  </si>
+  <si>
+    <t>佩佩</t>
+  </si>
+  <si>
+    <t>娜仁图亚</t>
+  </si>
+  <si>
+    <t>荒芜拉普兰德</t>
+  </si>
+  <si>
+    <t>玛露西尔</t>
+  </si>
+  <si>
+    <t>WAH-X</t>
+  </si>
+  <si>
+    <t>弑君者</t>
+  </si>
+  <si>
+    <t>引星棘刺</t>
+  </si>
+  <si>
+    <t>SOL-X</t>
+  </si>
+  <si>
+    <t>BAR-X</t>
+  </si>
+  <si>
+    <t>RIT-X</t>
+  </si>
+  <si>
+    <t>WDM-X</t>
+  </si>
+  <si>
+    <t>CRU-X</t>
+  </si>
+  <si>
+    <t>AFT-X</t>
+  </si>
+  <si>
+    <t>维娜·维多利亚</t>
+  </si>
+  <si>
+    <t>AFT-Δ</t>
+  </si>
+  <si>
+    <t>ISW-A</t>
+  </si>
+  <si>
+    <t>HAM-X</t>
+  </si>
+  <si>
+    <t>RA-A</t>
+  </si>
+  <si>
+    <t>余</t>
+  </si>
+  <si>
+    <t>BLA-D</t>
+  </si>
+  <si>
+    <t>烛煌</t>
+  </si>
+  <si>
+    <t>PUS-Y</t>
+  </si>
+  <si>
+    <t>BEA-Y</t>
+  </si>
+  <si>
+    <t>AGE-Y</t>
+  </si>
+  <si>
+    <t>重岳</t>
+  </si>
+  <si>
+    <t>LIB-X</t>
+  </si>
+  <si>
+    <t>隐德来希</t>
+  </si>
+  <si>
+    <t>信仰搅拌机</t>
+  </si>
+  <si>
+    <t>鸿雪</t>
+  </si>
+  <si>
+    <t>蕾缪安</t>
+  </si>
+  <si>
+    <t>DEA-Y</t>
+  </si>
+  <si>
+    <t>死芒</t>
+  </si>
+  <si>
+    <t>Mon3tr</t>
+  </si>
+  <si>
+    <t>新约能天使</t>
+  </si>
+  <si>
+    <t>GEE-X</t>
+  </si>
+  <si>
+    <t>ALC-X</t>
+  </si>
+  <si>
+    <t>司霆惊蛰</t>
+  </si>
+  <si>
     <t>PRO-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>四五星三技能填0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不填则随机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模组名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模组等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白铁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOL-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOL-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伺夜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斥罪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缄默德克萨斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUM-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SIE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>焰影苇草</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCR-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仇白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麒麟X夜刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUS-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伊内丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLX-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRP-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缪尔赛思</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>霍尔海雅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淬羽赫默</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BOM-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UMD-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣约送葬人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩业星熊</t>
+  </si>
+  <si>
+    <t>RPR-Y</t>
+  </si>
+  <si>
+    <t>FUN-Y</t>
+  </si>
+  <si>
+    <t>CCR-Y</t>
+  </si>
+  <si>
+    <t>SPC-X</t>
+  </si>
+  <si>
+    <t>PRI-X</t>
+  </si>
+  <si>
+    <t>SOC-X</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>SO-A</t>
+  </si>
+  <si>
+    <t>酒神</t>
+  </si>
+  <si>
+    <t>遥</t>
+  </si>
+  <si>
+    <t>BLS-Y</t>
+  </si>
+  <si>
+    <t>EXE-Y</t>
+  </si>
+  <si>
+    <t>可露希尔</t>
+  </si>
+  <si>
+    <t>凛御银灰</t>
+  </si>
+  <si>
+    <t>贝洛内</t>
+  </si>
+  <si>
+    <t>赤刃明霄陈</t>
+  </si>
+  <si>
+    <t>丰川祥子</t>
+  </si>
+  <si>
+    <t>LOR-Y</t>
+  </si>
+  <si>
+    <t>怒潮凛冬</t>
+  </si>
+  <si>
+    <t>AFT-Y</t>
+  </si>
+  <si>
+    <t>REA-Y</t>
+  </si>
+  <si>
+    <t>PRO-Y</t>
+  </si>
+  <si>
+    <t>PRP-X</t>
+  </si>
+  <si>
+    <t>AST-X</t>
+  </si>
+  <si>
+    <t>LPS-X</t>
+  </si>
+  <si>
+    <t>圣聆初雪</t>
+  </si>
+  <si>
+    <t>PLX-Y</t>
+  </si>
+  <si>
+    <t>SPC-Y</t>
+  </si>
+  <si>
+    <t>真言</t>
+  </si>
+  <si>
+    <t>凯尔希·思衡托</t>
+  </si>
+  <si>
+    <t>XAH-X</t>
+  </si>
+  <si>
+    <t>缇缇</t>
+  </si>
+  <si>
+    <t>RIN-Y</t>
+  </si>
+  <si>
+    <t>SO-B</t>
+  </si>
+  <si>
+    <t>娜斯提</t>
   </si>
   <si>
     <t>CRA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GEE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BEA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提丰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SIE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琳琅诗怀雅</t>
-  </si>
-  <si>
-    <t>MER-X</t>
-  </si>
-  <si>
-    <t>CEN-X</t>
-  </si>
-  <si>
-    <t>REA-X</t>
-  </si>
-  <si>
-    <t>纯烬艾雅法拉</t>
-  </si>
-  <si>
-    <t>涤火杰西卡</t>
-  </si>
-  <si>
-    <t>BLS-X</t>
-  </si>
-  <si>
-    <t>赫德雷</t>
-  </si>
-  <si>
-    <t>FOR-X</t>
-  </si>
-  <si>
-    <t>ARC-X</t>
-  </si>
-  <si>
-    <t>薇薇安娜</t>
-  </si>
-  <si>
-    <t>止颂</t>
-  </si>
-  <si>
-    <t>UNY-X</t>
-  </si>
-  <si>
-    <t>塑心</t>
-  </si>
-  <si>
-    <t>锏</t>
-  </si>
-  <si>
-    <t>FUN-X</t>
-  </si>
-  <si>
-    <t>INC-X</t>
-  </si>
-  <si>
-    <t>DEC-Y</t>
-  </si>
-  <si>
-    <t>莱伊</t>
-  </si>
-  <si>
-    <t>FGT-Y</t>
-  </si>
-  <si>
-    <t>FGT-X</t>
-  </si>
-  <si>
-    <t>左乐</t>
-  </si>
-  <si>
-    <t>黍</t>
-  </si>
-  <si>
-    <t>SBL-X</t>
-  </si>
-  <si>
-    <t>GUA-X</t>
-  </si>
-  <si>
-    <t>SPT-X</t>
-  </si>
-  <si>
-    <t>艾拉</t>
-  </si>
-  <si>
-    <t>TRP-Δ</t>
-  </si>
-  <si>
-    <t>TAC-X</t>
-  </si>
-  <si>
-    <t>阿斯卡纶</t>
-  </si>
-  <si>
-    <t>LOR-X</t>
-  </si>
-  <si>
-    <t>维什戴尔</t>
-  </si>
-  <si>
-    <t>BOM-X</t>
-  </si>
-  <si>
-    <t>逻各斯</t>
-  </si>
-  <si>
-    <t>魔王</t>
-  </si>
-  <si>
-    <t>CCR-X</t>
-  </si>
-  <si>
-    <t>CCR-Δ</t>
-  </si>
-  <si>
-    <t>乌尔比安</t>
-  </si>
-  <si>
-    <t>HUN-X</t>
-  </si>
-  <si>
-    <t>2019.05.06</t>
-  </si>
-  <si>
-    <t>妮芙</t>
-  </si>
-  <si>
-    <t>RPR-X</t>
-  </si>
-  <si>
-    <t>忍冬</t>
-  </si>
-  <si>
-    <t>佩佩</t>
-  </si>
-  <si>
-    <t>娜仁图亚</t>
-  </si>
-  <si>
-    <t>荒芜拉普兰德</t>
-  </si>
-  <si>
-    <t>玛露西尔</t>
-  </si>
-  <si>
-    <t>WAH-X</t>
-  </si>
-  <si>
-    <t>弑君者</t>
-  </si>
-  <si>
-    <t>引星棘刺</t>
-  </si>
-  <si>
-    <t>SOL-X</t>
-  </si>
-  <si>
-    <t>BAR-X</t>
-  </si>
-  <si>
-    <t>RIT-X</t>
-  </si>
-  <si>
-    <t>WDM-X</t>
-  </si>
-  <si>
-    <t>CRU-X</t>
-  </si>
-  <si>
-    <t>AFT-X</t>
-  </si>
-  <si>
-    <t>维娜·维多利亚</t>
-  </si>
-  <si>
-    <t>AFT-Δ</t>
-  </si>
-  <si>
-    <t>ISW-A</t>
-  </si>
-  <si>
-    <t>HAM-X</t>
-  </si>
-  <si>
-    <t>RA-A</t>
-  </si>
-  <si>
-    <t>余</t>
-  </si>
-  <si>
-    <t>BLA-D</t>
-  </si>
-  <si>
-    <t>烛煌</t>
-  </si>
-  <si>
-    <t>PUS-Y</t>
-  </si>
-  <si>
-    <t>BEA-Y</t>
-  </si>
-  <si>
-    <t>AGE-Y</t>
-  </si>
-  <si>
-    <t>重岳</t>
-  </si>
-  <si>
-    <t>LIB-X</t>
-  </si>
-  <si>
-    <t>隐德来希</t>
-  </si>
-  <si>
-    <t>信仰搅拌机</t>
-  </si>
-  <si>
-    <t>鸿雪</t>
-  </si>
-  <si>
-    <t>蕾缪安</t>
-  </si>
-  <si>
-    <t>DEA-Y</t>
-  </si>
-  <si>
-    <t>死芒</t>
-  </si>
-  <si>
-    <t>Mon3tr</t>
-  </si>
-  <si>
-    <t>新约能天使</t>
-  </si>
-  <si>
-    <t>GEE-X</t>
-  </si>
-  <si>
-    <t>ALC-X</t>
-  </si>
-  <si>
-    <t>2025.08.09</t>
-  </si>
-  <si>
-    <t>司霆惊蛰</t>
-  </si>
-  <si>
-    <t>PRO-X</t>
-  </si>
-  <si>
-    <t>斩业星熊</t>
-  </si>
-  <si>
-    <t>RPR-Y</t>
-  </si>
-  <si>
-    <t>FUN-Y</t>
-  </si>
-  <si>
-    <t>CCR-Y</t>
-  </si>
-  <si>
-    <t>SPC-X</t>
-  </si>
-  <si>
-    <t>PRI-X</t>
-  </si>
-  <si>
-    <t>SOC-X</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>SO-A</t>
-  </si>
-  <si>
-    <t>酒神</t>
-  </si>
-  <si>
-    <t>遥</t>
-  </si>
-  <si>
-    <t>BLS-Y</t>
-  </si>
-  <si>
-    <t>EXE-Y</t>
+  </si>
+  <si>
+    <t>溯光星源</t>
+  </si>
+  <si>
+    <t>BAR-Y</t>
+  </si>
+  <si>
+    <t>elite0</t>
+  </si>
+  <si>
+    <t>望</t>
+  </si>
+  <si>
+    <t>TRP-X</t>
+  </si>
+  <si>
+    <t>2026.05.02</t>
   </si>
 </sst>
 </file>
@@ -1089,14 +1172,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1393,9 +1476,9 @@
       <c r="B1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -1404,16 +1487,16 @@
       <c r="B2" s="2">
         <v>1618440</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1421,7 +1504,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>253</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1437,7 +1520,7 @@
         <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1535,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.1328125" customWidth="1"/>
@@ -1547,28 +1630,28 @@
       <c r="A1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="16"/>
+      <c r="C1" s="15"/>
       <c r="D1" s="11"/>
       <c r="E1" s="12"/>
-      <c r="F1" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="F1" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="9" t="s">
         <v>55</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="L1" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1676,7 +1759,7 @@
         <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1725,13 +1808,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1749,13 +1832,13 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>108</v>
@@ -1763,13 +1846,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>268</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1787,27 +1870,18 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" t="s">
-        <v>171</v>
-      </c>
-      <c r="K7">
-        <v>3</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1828,24 +1902,24 @@
         <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="K8">
         <v>3</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1863,21 +1937,21 @@
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1901,27 +1975,27 @@
         <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J10" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>215</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1939,10 +2013,10 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J11" t="s">
-        <v>145</v>
+        <v>223</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1953,13 +2027,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1980,18 +2054,18 @@
         <v>57</v>
       </c>
       <c r="J12" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -2018,24 +2092,24 @@
         <v>58</v>
       </c>
       <c r="J13" t="s">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2053,27 +2127,27 @@
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J14" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="B15">
         <v>6</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2091,27 +2165,27 @@
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J15" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2129,10 +2203,10 @@
         <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2143,7 +2217,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2170,24 +2244,24 @@
         <v>58</v>
       </c>
       <c r="J17" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="K17">
         <v>3</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="B18">
         <v>6</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2208,24 +2282,24 @@
         <v>57</v>
       </c>
       <c r="J18" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2243,27 +2317,27 @@
         <v>10</v>
       </c>
       <c r="I19" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J19" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2284,7 +2358,7 @@
         <v>58</v>
       </c>
       <c r="J20" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2295,7 +2369,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -2319,10 +2393,10 @@
         <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J21" t="s">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -2333,7 +2407,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="B22">
         <v>6</v>
@@ -2360,24 +2434,24 @@
         <v>58</v>
       </c>
       <c r="J22" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="K22">
         <v>3</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>271</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2395,21 +2469,21 @@
         <v>10</v>
       </c>
       <c r="I23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J23" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="K23">
         <v>3</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -2436,24 +2510,24 @@
         <v>57</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>1</v>
       </c>
       <c r="B25">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2471,27 +2545,27 @@
         <v>10</v>
       </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J25" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>2</v>
       </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2509,21 +2583,21 @@
         <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J26" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -2547,13 +2621,13 @@
         <v>10</v>
       </c>
       <c r="I27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J27" t="s">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>105</v>
@@ -2561,7 +2635,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -2588,10 +2662,10 @@
         <v>58</v>
       </c>
       <c r="J28" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>105</v>
@@ -2599,13 +2673,13 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2623,27 +2697,27 @@
         <v>10</v>
       </c>
       <c r="I29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J29" t="s">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>273</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -2661,10 +2735,10 @@
         <v>10</v>
       </c>
       <c r="I30" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J30" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -2675,13 +2749,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B31">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2702,10 +2776,10 @@
         <v>57</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>105</v>
@@ -2713,13 +2787,13 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>216</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -2737,27 +2811,27 @@
         <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J32" t="s">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2775,27 +2849,27 @@
         <v>10</v>
       </c>
       <c r="I33" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J33" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>230</v>
+        <v>153</v>
       </c>
       <c r="B34">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -2813,13 +2887,13 @@
         <v>10</v>
       </c>
       <c r="I34" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J34" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="K34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>105</v>
@@ -2827,13 +2901,13 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -2851,13 +2925,13 @@
         <v>10</v>
       </c>
       <c r="I35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J35" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>105</v>
@@ -2865,13 +2939,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -2889,13 +2963,13 @@
         <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J36" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>107</v>
@@ -2903,7 +2977,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -2930,7 +3004,7 @@
         <v>57</v>
       </c>
       <c r="J37" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -2941,13 +3015,13 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>243</v>
+        <v>6</v>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2965,21 +3039,21 @@
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J38" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B39">
         <v>6</v>
@@ -3003,10 +3077,10 @@
         <v>10</v>
       </c>
       <c r="I39" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J39" t="s">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -3017,7 +3091,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -3041,21 +3115,21 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="B41">
         <v>6</v>
@@ -3082,24 +3156,24 @@
         <v>57</v>
       </c>
       <c r="J41" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>229</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -3117,27 +3191,27 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="K42">
         <v>3</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3158,24 +3232,24 @@
         <v>57</v>
       </c>
       <c r="J43" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -3196,24 +3270,24 @@
         <v>57</v>
       </c>
       <c r="J44" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="K44">
         <v>3</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -3231,27 +3305,27 @@
         <v>10</v>
       </c>
       <c r="I45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J45" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="K45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>242</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -3269,27 +3343,27 @@
         <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="J46" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="K46">
         <v>3</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -3310,18 +3384,18 @@
         <v>57</v>
       </c>
       <c r="J47" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="K47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B48">
         <v>6</v>
@@ -3345,21 +3419,21 @@
         <v>10</v>
       </c>
       <c r="I48" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="J48" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -3386,56 +3460,56 @@
         <v>57</v>
       </c>
       <c r="J49" t="s">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="K49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
+        <v>194</v>
+      </c>
+      <c r="B50">
+        <v>6</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50">
+        <v>90</v>
+      </c>
+      <c r="F50">
+        <v>10</v>
+      </c>
+      <c r="G50">
+        <v>10</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+      <c r="I50" t="s">
+        <v>58</v>
+      </c>
+      <c r="J50" t="s">
         <v>196</v>
       </c>
-      <c r="B50">
-        <v>6</v>
-      </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50">
-        <v>2</v>
-      </c>
-      <c r="E50">
-        <v>90</v>
-      </c>
-      <c r="F50">
-        <v>10</v>
-      </c>
-      <c r="G50">
-        <v>10</v>
-      </c>
-      <c r="H50">
-        <v>10</v>
-      </c>
-      <c r="I50" t="s">
-        <v>57</v>
-      </c>
-      <c r="J50" t="s">
-        <v>198</v>
-      </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="B51">
         <v>6</v>
@@ -3459,13 +3533,13 @@
         <v>10</v>
       </c>
       <c r="I51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J51" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>108</v>
@@ -3473,13 +3547,13 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -3500,7 +3574,7 @@
         <v>57</v>
       </c>
       <c r="J52" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3511,13 +3585,13 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -3535,27 +3609,27 @@
         <v>10</v>
       </c>
       <c r="I53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J53" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -3573,27 +3647,27 @@
         <v>10</v>
       </c>
       <c r="I54" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J54" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="K54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>235</v>
+        <v>17</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3611,12 +3685,21 @@
         <v>10</v>
       </c>
       <c r="I55" t="s">
-        <v>109</v>
+        <v>58</v>
+      </c>
+      <c r="J55" t="s">
+        <v>276</v>
+      </c>
+      <c r="K55">
+        <v>3</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>256</v>
+        <v>16</v>
       </c>
       <c r="B56">
         <v>6</v>
@@ -3640,18 +3723,27 @@
         <v>10</v>
       </c>
       <c r="I56" t="s">
-        <v>109</v>
+        <v>132</v>
+      </c>
+      <c r="J56" t="s">
+        <v>185</v>
+      </c>
+      <c r="K56">
+        <v>3</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3669,21 +3761,21 @@
         <v>10</v>
       </c>
       <c r="I57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J57" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B58">
         <v>6</v>
@@ -3707,21 +3799,21 @@
         <v>10</v>
       </c>
       <c r="I58" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J58" t="s">
-        <v>183</v>
+        <v>87</v>
       </c>
       <c r="K58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="B59">
         <v>6</v>
@@ -3745,21 +3837,21 @@
         <v>10</v>
       </c>
       <c r="I59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J59" t="s">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="K59">
         <v>3</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>245</v>
+        <v>195</v>
       </c>
       <c r="B60">
         <v>6</v>
@@ -3783,27 +3875,27 @@
         <v>10</v>
       </c>
       <c r="I60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J60" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="K60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -3824,24 +3916,24 @@
         <v>57</v>
       </c>
       <c r="J61" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="K61">
         <v>1</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3862,24 +3954,24 @@
         <v>57</v>
       </c>
       <c r="J62" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="K62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63">
         <v>6</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -3900,24 +3992,24 @@
         <v>58</v>
       </c>
       <c r="J63" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>243</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -3935,27 +4027,27 @@
         <v>10</v>
       </c>
       <c r="I64" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J64" t="s">
-        <v>126</v>
+        <v>198</v>
       </c>
       <c r="K64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>234</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3973,10 +4065,10 @@
         <v>10</v>
       </c>
       <c r="I65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J65" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="K65">
         <v>3</v>
@@ -3987,13 +4079,13 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -4011,21 +4103,21 @@
         <v>10</v>
       </c>
       <c r="I66" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J66" t="s">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>246</v>
+        <v>70</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -4049,13 +4141,13 @@
         <v>10</v>
       </c>
       <c r="I67" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J67" t="s">
-        <v>247</v>
+        <v>90</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>105</v>
@@ -4063,13 +4155,13 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -4087,27 +4179,27 @@
         <v>10</v>
       </c>
       <c r="I68" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J68" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="K68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B69">
         <v>6</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -4125,27 +4217,27 @@
         <v>10</v>
       </c>
       <c r="I69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J69" t="s">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="B70">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -4163,18 +4255,27 @@
         <v>10</v>
       </c>
       <c r="I70" t="s">
-        <v>109</v>
+        <v>58</v>
+      </c>
+      <c r="J70" t="s">
+        <v>133</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4192,10 +4293,10 @@
         <v>10</v>
       </c>
       <c r="I71" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -4206,13 +4307,13 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="B72">
         <v>6</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -4230,10 +4331,10 @@
         <v>10</v>
       </c>
       <c r="I72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J72" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="K72">
         <v>3</v>
@@ -4244,13 +4345,13 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B73">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -4268,21 +4369,21 @@
         <v>10</v>
       </c>
       <c r="I73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J73" t="s">
-        <v>89</v>
+        <v>255</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>205</v>
+        <v>13</v>
       </c>
       <c r="B74">
         <v>6</v>
@@ -4309,7 +4410,7 @@
         <v>57</v>
       </c>
       <c r="J74" t="s">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="K74">
         <v>3</v>
@@ -4320,13 +4421,13 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="B75">
         <v>6</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -4344,13 +4445,13 @@
         <v>10</v>
       </c>
       <c r="I75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J75" t="s">
-        <v>91</v>
+        <v>231</v>
       </c>
       <c r="K75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>105</v>
@@ -4358,13 +4459,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="B76">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4385,24 +4486,24 @@
         <v>57</v>
       </c>
       <c r="J76" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="K76">
         <v>3</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="B77">
         <v>6</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <v>2</v>
@@ -4423,7 +4524,7 @@
         <v>57</v>
       </c>
       <c r="J77" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="K77">
         <v>3</v>
@@ -4434,13 +4535,13 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B78">
         <v>6</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4458,13 +4559,13 @@
         <v>10</v>
       </c>
       <c r="I78" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="J78" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>105</v>
@@ -4472,13 +4573,13 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B79">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4499,24 +4600,24 @@
         <v>58</v>
       </c>
       <c r="J79" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="K79">
         <v>3</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="B80">
         <v>6</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -4534,13 +4635,13 @@
         <v>10</v>
       </c>
       <c r="I80" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J80" t="s">
-        <v>92</v>
+        <v>279</v>
       </c>
       <c r="K80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>105</v>
@@ -4548,7 +4649,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>219</v>
+        <v>15</v>
       </c>
       <c r="B81">
         <v>6</v>
@@ -4572,13 +4673,13 @@
         <v>10</v>
       </c>
       <c r="I81" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="J81" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="K81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>105</v>
@@ -4586,7 +4687,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B82">
         <v>6</v>
@@ -4613,10 +4714,10 @@
         <v>57</v>
       </c>
       <c r="J82" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>105</v>
@@ -4624,7 +4725,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B83">
         <v>6</v>
@@ -4648,10 +4749,10 @@
         <v>10</v>
       </c>
       <c r="I83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J83" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="K83">
         <v>3</v>
@@ -4662,13 +4763,13 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B84">
         <v>6</v>
       </c>
       <c r="C84">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4686,27 +4787,27 @@
         <v>10</v>
       </c>
       <c r="I84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J84" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="K84">
         <v>1</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="B85">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4727,7 +4828,7 @@
         <v>58</v>
       </c>
       <c r="J85" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K85">
         <v>3</v>
@@ -4738,13 +4839,13 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="B86">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -4762,27 +4863,27 @@
         <v>10</v>
       </c>
       <c r="I86" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J86" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="B87">
         <v>6</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D87">
         <v>2</v>
@@ -4800,10 +4901,10 @@
         <v>10</v>
       </c>
       <c r="I87" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J87" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="K87">
         <v>3</v>
@@ -4814,13 +4915,13 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
       <c r="B88">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -4838,21 +4939,21 @@
         <v>10</v>
       </c>
       <c r="I88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J88" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B89">
         <v>6</v>
@@ -4876,10 +4977,10 @@
         <v>10</v>
       </c>
       <c r="I89" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J89" t="s">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="K89">
         <v>3</v>
@@ -4890,7 +4991,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B90">
         <v>6</v>
@@ -4914,27 +5015,27 @@
         <v>10</v>
       </c>
       <c r="I90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J90" t="s">
-        <v>93</v>
+        <v>256</v>
       </c>
       <c r="K90">
         <v>3</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="B91">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -4955,7 +5056,7 @@
         <v>57</v>
       </c>
       <c r="J91" t="s">
-        <v>261</v>
+        <v>92</v>
       </c>
       <c r="K91">
         <v>1</v>
@@ -4966,13 +5067,13 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="B92">
         <v>6</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4993,24 +5094,24 @@
         <v>57</v>
       </c>
       <c r="J92" t="s">
-        <v>262</v>
+        <v>188</v>
       </c>
       <c r="K92">
         <v>3</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="B93">
         <v>6</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -5028,10 +5129,10 @@
         <v>10</v>
       </c>
       <c r="I93" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J93" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="K93">
         <v>1</v>
@@ -5042,13 +5143,13 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="B94">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -5069,18 +5170,18 @@
         <v>57</v>
       </c>
       <c r="J94" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="K94">
         <v>3</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="B95">
         <v>6</v>
@@ -5104,21 +5205,21 @@
         <v>10</v>
       </c>
       <c r="I95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J95" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="K95">
         <v>3</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B96">
         <v>6</v>
@@ -5145,24 +5246,24 @@
         <v>58</v>
       </c>
       <c r="J96" t="s">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="K96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5180,13 +5281,13 @@
         <v>10</v>
       </c>
       <c r="I97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J97" t="s">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c r="K97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>105</v>
@@ -5194,13 +5295,13 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>237</v>
+        <v>152</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5218,27 +5319,27 @@
         <v>10</v>
       </c>
       <c r="I98" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J98" t="s">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="B99">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5259,24 +5360,24 @@
         <v>57</v>
       </c>
       <c r="J99" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="K99">
         <v>3</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="B100">
         <v>6</v>
       </c>
       <c r="C100">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -5294,21 +5395,21 @@
         <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J100" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B101">
         <v>6</v>
@@ -5332,21 +5433,21 @@
         <v>10</v>
       </c>
       <c r="I101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J101" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B102">
         <v>6</v>
@@ -5373,24 +5474,24 @@
         <v>57</v>
       </c>
       <c r="J102" t="s">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="K102">
         <v>3</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="B103">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -5408,27 +5509,27 @@
         <v>10</v>
       </c>
       <c r="I103" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J103" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="K103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="B104">
         <v>6</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5448,16 +5549,25 @@
       <c r="I104" t="s">
         <v>109</v>
       </c>
+      <c r="J104" t="s">
+        <v>281</v>
+      </c>
+      <c r="K104">
+        <v>3</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>247</v>
       </c>
       <c r="B105">
         <v>6</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5475,27 +5585,27 @@
         <v>10</v>
       </c>
       <c r="I105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J105" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="K105">
         <v>3</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>151</v>
+        <v>30</v>
       </c>
       <c r="B106">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5513,27 +5623,27 @@
         <v>10</v>
       </c>
       <c r="I106" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J106" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="K106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B107">
         <v>6</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5551,27 +5661,27 @@
         <v>10</v>
       </c>
       <c r="I107" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J107" t="s">
-        <v>96</v>
+        <v>282</v>
       </c>
       <c r="K107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B108">
         <v>6</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -5589,21 +5699,21 @@
         <v>10</v>
       </c>
       <c r="I108" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J108" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="K108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B109">
         <v>6</v>
@@ -5627,27 +5737,27 @@
         <v>10</v>
       </c>
       <c r="I109" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J109" t="s">
-        <v>232</v>
+        <v>156</v>
       </c>
       <c r="K109">
         <v>3</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="B110">
         <v>6</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -5665,27 +5775,27 @@
         <v>10</v>
       </c>
       <c r="I110" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J110" t="s">
-        <v>169</v>
+        <v>235</v>
       </c>
       <c r="K110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>163</v>
+        <v>32</v>
       </c>
       <c r="B111">
         <v>6</v>
       </c>
       <c r="C111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -5703,27 +5813,27 @@
         <v>10</v>
       </c>
       <c r="I111" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J111" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="K111">
         <v>1</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>263</v>
+        <v>32</v>
       </c>
       <c r="B112">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -5741,10 +5851,10 @@
         <v>10</v>
       </c>
       <c r="I112" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J112" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="K112">
         <v>3</v>
@@ -5755,13 +5865,13 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B113">
         <v>6</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5782,7 +5892,7 @@
         <v>109</v>
       </c>
       <c r="J113" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="K113">
         <v>3</v>
@@ -5793,13 +5903,13 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="B114">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -5817,27 +5927,27 @@
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J114" t="s">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="K114">
         <v>3</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="B115">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -5855,21 +5965,21 @@
         <v>10</v>
       </c>
       <c r="I115" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J115" t="s">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="K115">
         <v>3</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B116">
         <v>6</v>
@@ -5893,27 +6003,27 @@
         <v>10</v>
       </c>
       <c r="I116" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="J116" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B117">
         <v>6</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -5934,18 +6044,18 @@
         <v>57</v>
       </c>
       <c r="J117" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K117">
         <v>3</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -5969,27 +6079,27 @@
         <v>10</v>
       </c>
       <c r="I118" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J118" t="s">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="K118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="B119">
         <v>6</v>
       </c>
       <c r="C119">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -6009,19 +6119,10 @@
       <c r="I119" t="s">
         <v>109</v>
       </c>
-      <c r="J119" t="s">
-        <v>225</v>
-      </c>
-      <c r="K119">
-        <v>3</v>
-      </c>
-      <c r="L119" s="8" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="B120">
         <v>6</v>
@@ -6045,27 +6146,27 @@
         <v>10</v>
       </c>
       <c r="I120" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J120" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B121">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -6083,21 +6184,21 @@
         <v>10</v>
       </c>
       <c r="I121" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="J121" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="K121">
         <v>3</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B122">
         <v>6</v>
@@ -6121,27 +6222,27 @@
         <v>10</v>
       </c>
       <c r="I122" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J122" t="s">
-        <v>225</v>
+        <v>141</v>
       </c>
       <c r="K122">
         <v>3</v>
       </c>
       <c r="L122" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
       <c r="B123">
         <v>6</v>
       </c>
       <c r="C123">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -6159,27 +6260,27 @@
         <v>10</v>
       </c>
       <c r="I123" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J123" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B124">
         <v>6</v>
       </c>
       <c r="C124">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -6197,27 +6298,27 @@
         <v>10</v>
       </c>
       <c r="I124" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="J124" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="K124">
         <v>3</v>
       </c>
       <c r="L124" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="B125">
         <v>6</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -6238,18 +6339,18 @@
         <v>57</v>
       </c>
       <c r="J125" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="K125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L125" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="B126">
         <v>6</v>
@@ -6273,21 +6374,21 @@
         <v>10</v>
       </c>
       <c r="I126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J126" t="s">
-        <v>160</v>
+        <v>287</v>
       </c>
       <c r="K126">
         <v>3</v>
       </c>
       <c r="L126" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B127">
         <v>6</v>
@@ -6311,21 +6412,21 @@
         <v>10</v>
       </c>
       <c r="I127" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J127" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="K127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L127" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -6349,27 +6450,27 @@
         <v>10</v>
       </c>
       <c r="I128" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J128" t="s">
-        <v>101</v>
+        <v>231</v>
       </c>
       <c r="K128">
         <v>3</v>
       </c>
       <c r="L128" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="B129">
         <v>6</v>
       </c>
       <c r="C129">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -6387,21 +6488,21 @@
         <v>10</v>
       </c>
       <c r="I129" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J129" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="K129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L129" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B130">
         <v>6</v>
@@ -6425,21 +6526,21 @@
         <v>10</v>
       </c>
       <c r="I130" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J130" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="K130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L130" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="B131">
         <v>6</v>
@@ -6463,21 +6564,21 @@
         <v>10</v>
       </c>
       <c r="I131" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J131" t="s">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L131" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="B132">
         <v>6</v>
@@ -6501,10 +6602,10 @@
         <v>10</v>
       </c>
       <c r="I132" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J132" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="K132">
         <v>3</v>
@@ -6515,13 +6616,13 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="B133">
         <v>6</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -6539,27 +6640,27 @@
         <v>10</v>
       </c>
       <c r="I133" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J133" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L133" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="B134">
         <v>6</v>
       </c>
       <c r="C134">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -6577,13 +6678,13 @@
         <v>10</v>
       </c>
       <c r="I134" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="J134" t="s">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="K134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>106</v>
@@ -6591,7 +6692,7 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="B135">
         <v>6</v>
@@ -6615,10 +6716,10 @@
         <v>10</v>
       </c>
       <c r="I135" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="J135" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K135">
         <v>3</v>
@@ -6629,7 +6730,7 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="B136">
         <v>6</v>
@@ -6653,13 +6754,13 @@
         <v>10</v>
       </c>
       <c r="I136" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="J136" t="s">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="K136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>106</v>
@@ -6667,13 +6768,13 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>222</v>
+        <v>23</v>
       </c>
       <c r="B137">
         <v>6</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -6694,24 +6795,24 @@
         <v>109</v>
       </c>
       <c r="J137" t="s">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="K137">
         <v>3</v>
       </c>
       <c r="L137" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B138">
         <v>6</v>
       </c>
       <c r="C138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -6732,24 +6833,24 @@
         <v>57</v>
       </c>
       <c r="J138" t="s">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="K138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L138" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B139">
         <v>6</v>
       </c>
       <c r="C139">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -6767,21 +6868,21 @@
         <v>10</v>
       </c>
       <c r="I139" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J139" t="s">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="K139">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L139" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="B140">
         <v>6</v>
@@ -6808,24 +6909,24 @@
         <v>57</v>
       </c>
       <c r="J140" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="K140">
         <v>3</v>
       </c>
       <c r="L140" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>289</v>
       </c>
       <c r="B141">
         <v>6</v>
       </c>
       <c r="C141">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -6843,13 +6944,13 @@
         <v>10</v>
       </c>
       <c r="I141" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="J141" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="K141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L141" s="8" t="s">
         <v>106</v>
@@ -6857,13 +6958,13 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="B142">
         <v>6</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -6884,10 +6985,10 @@
         <v>109</v>
       </c>
       <c r="J142" t="s">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="K142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>106</v>
@@ -6895,13 +6996,13 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="B143">
         <v>6</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -6922,17 +7023,1043 @@
         <v>57</v>
       </c>
       <c r="J143" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="K143">
         <v>3</v>
       </c>
       <c r="L143" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" t="s">
+        <v>264</v>
+      </c>
+      <c r="B144">
+        <v>6</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>2</v>
+      </c>
+      <c r="E144">
+        <v>90</v>
+      </c>
+      <c r="F144">
+        <v>10</v>
+      </c>
+      <c r="G144">
+        <v>10</v>
+      </c>
+      <c r="H144">
+        <v>10</v>
+      </c>
+      <c r="I144" t="s">
+        <v>57</v>
+      </c>
+      <c r="J144" t="s">
+        <v>265</v>
+      </c>
+      <c r="K144">
+        <v>3</v>
+      </c>
+      <c r="L144" s="8" t="s">
         <v>106</v>
       </c>
     </row>
+    <row r="145" spans="1:12">
+      <c r="A145" t="s">
+        <v>26</v>
+      </c>
+      <c r="B145">
+        <v>6</v>
+      </c>
+      <c r="C145">
+        <v>6</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+      <c r="E145">
+        <v>90</v>
+      </c>
+      <c r="F145">
+        <v>10</v>
+      </c>
+      <c r="G145">
+        <v>10</v>
+      </c>
+      <c r="H145">
+        <v>10</v>
+      </c>
+      <c r="I145" t="s">
+        <v>57</v>
+      </c>
+      <c r="J145" t="s">
+        <v>224</v>
+      </c>
+      <c r="K145">
+        <v>3</v>
+      </c>
+      <c r="L145" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146" t="s">
+        <v>26</v>
+      </c>
+      <c r="B146">
+        <v>6</v>
+      </c>
+      <c r="C146">
+        <v>6</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146">
+        <v>90</v>
+      </c>
+      <c r="F146">
+        <v>10</v>
+      </c>
+      <c r="G146">
+        <v>10</v>
+      </c>
+      <c r="H146">
+        <v>10</v>
+      </c>
+      <c r="I146" t="s">
+        <v>58</v>
+      </c>
+      <c r="J146" t="s">
+        <v>292</v>
+      </c>
+      <c r="K146">
+        <v>3</v>
+      </c>
+      <c r="L146" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147" t="s">
+        <v>33</v>
+      </c>
+      <c r="B147">
+        <v>6</v>
+      </c>
+      <c r="C147">
+        <v>5</v>
+      </c>
+      <c r="D147">
+        <v>2</v>
+      </c>
+      <c r="E147">
+        <v>90</v>
+      </c>
+      <c r="F147">
+        <v>10</v>
+      </c>
+      <c r="G147">
+        <v>10</v>
+      </c>
+      <c r="H147">
+        <v>10</v>
+      </c>
+      <c r="I147" t="s">
+        <v>58</v>
+      </c>
+      <c r="J147" t="s">
+        <v>169</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148" t="s">
+        <v>199</v>
+      </c>
+      <c r="B148">
+        <v>6</v>
+      </c>
+      <c r="C148">
+        <v>6</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+      <c r="E148">
+        <v>90</v>
+      </c>
+      <c r="F148">
+        <v>10</v>
+      </c>
+      <c r="G148">
+        <v>10</v>
+      </c>
+      <c r="H148">
+        <v>10</v>
+      </c>
+      <c r="I148" t="s">
+        <v>57</v>
+      </c>
+      <c r="J148" t="s">
+        <v>200</v>
+      </c>
+      <c r="K148">
+        <v>3</v>
+      </c>
+      <c r="L148" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
+      <c r="A149" t="s">
+        <v>202</v>
+      </c>
+      <c r="B149">
+        <v>6</v>
+      </c>
+      <c r="C149">
+        <v>2</v>
+      </c>
+      <c r="D149">
+        <v>2</v>
+      </c>
+      <c r="E149">
+        <v>90</v>
+      </c>
+      <c r="F149">
+        <v>10</v>
+      </c>
+      <c r="G149">
+        <v>10</v>
+      </c>
+      <c r="H149">
+        <v>10</v>
+      </c>
+      <c r="I149" t="s">
+        <v>57</v>
+      </c>
+      <c r="J149" t="s">
+        <v>131</v>
+      </c>
+      <c r="K149">
+        <v>3</v>
+      </c>
+      <c r="L149" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150" t="s">
+        <v>128</v>
+      </c>
+      <c r="B150">
+        <v>6</v>
+      </c>
+      <c r="C150">
+        <v>6</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150">
+        <v>90</v>
+      </c>
+      <c r="F150">
+        <v>10</v>
+      </c>
+      <c r="G150">
+        <v>10</v>
+      </c>
+      <c r="H150">
+        <v>10</v>
+      </c>
+      <c r="I150" t="s">
+        <v>57</v>
+      </c>
+      <c r="J150" t="s">
+        <v>159</v>
+      </c>
+      <c r="K150">
+        <v>3</v>
+      </c>
+      <c r="L150" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151">
+        <v>6</v>
+      </c>
+      <c r="C151">
+        <v>6</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+      <c r="E151">
+        <v>90</v>
+      </c>
+      <c r="F151">
+        <v>10</v>
+      </c>
+      <c r="G151">
+        <v>10</v>
+      </c>
+      <c r="H151">
+        <v>10</v>
+      </c>
+      <c r="I151" t="s">
+        <v>58</v>
+      </c>
+      <c r="J151" t="s">
+        <v>130</v>
+      </c>
+      <c r="K151">
+        <v>3</v>
+      </c>
+      <c r="L151" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" t="s">
+        <v>54</v>
+      </c>
+      <c r="B152">
+        <v>6</v>
+      </c>
+      <c r="C152">
+        <v>6</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152">
+        <v>90</v>
+      </c>
+      <c r="F152">
+        <v>10</v>
+      </c>
+      <c r="G152">
+        <v>10</v>
+      </c>
+      <c r="H152">
+        <v>10</v>
+      </c>
+      <c r="I152" t="s">
+        <v>293</v>
+      </c>
+      <c r="J152" t="s">
+        <v>101</v>
+      </c>
+      <c r="K152">
+        <v>3</v>
+      </c>
+      <c r="L152" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" t="s">
+        <v>54</v>
+      </c>
+      <c r="B153">
+        <v>6</v>
+      </c>
+      <c r="C153">
+        <v>6</v>
+      </c>
+      <c r="D153">
+        <v>2</v>
+      </c>
+      <c r="E153">
+        <v>90</v>
+      </c>
+      <c r="F153">
+        <v>10</v>
+      </c>
+      <c r="G153">
+        <v>10</v>
+      </c>
+      <c r="H153">
+        <v>10</v>
+      </c>
+      <c r="I153" t="s">
+        <v>109</v>
+      </c>
+      <c r="J153" t="s">
+        <v>148</v>
+      </c>
+      <c r="K153">
+        <v>3</v>
+      </c>
+      <c r="L153" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154" t="s">
+        <v>54</v>
+      </c>
+      <c r="B154">
+        <v>6</v>
+      </c>
+      <c r="C154">
+        <v>6</v>
+      </c>
+      <c r="D154">
+        <v>2</v>
+      </c>
+      <c r="E154">
+        <v>90</v>
+      </c>
+      <c r="F154">
+        <v>10</v>
+      </c>
+      <c r="G154">
+        <v>10</v>
+      </c>
+      <c r="H154">
+        <v>10</v>
+      </c>
+      <c r="I154" t="s">
+        <v>57</v>
+      </c>
+      <c r="J154" t="s">
+        <v>231</v>
+      </c>
+      <c r="K154">
+        <v>3</v>
+      </c>
+      <c r="L154" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" t="s">
+        <v>147</v>
+      </c>
+      <c r="B155">
+        <v>6</v>
+      </c>
+      <c r="C155">
+        <v>6</v>
+      </c>
+      <c r="D155">
+        <v>2</v>
+      </c>
+      <c r="E155">
+        <v>90</v>
+      </c>
+      <c r="F155">
+        <v>10</v>
+      </c>
+      <c r="G155">
+        <v>10</v>
+      </c>
+      <c r="H155">
+        <v>10</v>
+      </c>
+      <c r="I155" t="s">
+        <v>58</v>
+      </c>
+      <c r="J155" t="s">
+        <v>103</v>
+      </c>
+      <c r="K155">
+        <v>3</v>
+      </c>
+      <c r="L155" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B156">
+        <v>6</v>
+      </c>
+      <c r="C156">
+        <v>6</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+      <c r="E156">
+        <v>90</v>
+      </c>
+      <c r="F156">
+        <v>10</v>
+      </c>
+      <c r="G156">
+        <v>10</v>
+      </c>
+      <c r="H156">
+        <v>10</v>
+      </c>
+      <c r="I156" t="s">
+        <v>57</v>
+      </c>
+      <c r="J156" t="s">
+        <v>102</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157" t="s">
+        <v>35</v>
+      </c>
+      <c r="B157">
+        <v>6</v>
+      </c>
+      <c r="C157">
+        <v>6</v>
+      </c>
+      <c r="D157">
+        <v>2</v>
+      </c>
+      <c r="E157">
+        <v>90</v>
+      </c>
+      <c r="F157">
+        <v>10</v>
+      </c>
+      <c r="G157">
+        <v>10</v>
+      </c>
+      <c r="H157">
+        <v>10</v>
+      </c>
+      <c r="I157" t="s">
+        <v>58</v>
+      </c>
+      <c r="J157" t="s">
+        <v>231</v>
+      </c>
+      <c r="K157">
+        <v>3</v>
+      </c>
+      <c r="L157" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158" t="s">
+        <v>79</v>
+      </c>
+      <c r="B158">
+        <v>6</v>
+      </c>
+      <c r="C158">
+        <v>4</v>
+      </c>
+      <c r="D158">
+        <v>2</v>
+      </c>
+      <c r="E158">
+        <v>90</v>
+      </c>
+      <c r="F158">
+        <v>10</v>
+      </c>
+      <c r="G158">
+        <v>10</v>
+      </c>
+      <c r="H158">
+        <v>10</v>
+      </c>
+      <c r="I158" t="s">
+        <v>132</v>
+      </c>
+      <c r="J158" t="s">
+        <v>174</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
+      <c r="A159" t="s">
+        <v>173</v>
+      </c>
+      <c r="B159">
+        <v>6</v>
+      </c>
+      <c r="C159">
+        <v>3</v>
+      </c>
+      <c r="D159">
+        <v>2</v>
+      </c>
+      <c r="E159">
+        <v>90</v>
+      </c>
+      <c r="F159">
+        <v>10</v>
+      </c>
+      <c r="G159">
+        <v>10</v>
+      </c>
+      <c r="H159">
+        <v>10</v>
+      </c>
+      <c r="I159" t="s">
+        <v>109</v>
+      </c>
+      <c r="J159" t="s">
+        <v>174</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" t="s">
+        <v>173</v>
+      </c>
+      <c r="B160">
+        <v>6</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+      <c r="D160">
+        <v>2</v>
+      </c>
+      <c r="E160">
+        <v>90</v>
+      </c>
+      <c r="F160">
+        <v>10</v>
+      </c>
+      <c r="G160">
+        <v>10</v>
+      </c>
+      <c r="H160">
+        <v>10</v>
+      </c>
+      <c r="I160" t="s">
+        <v>57</v>
+      </c>
+      <c r="J160" t="s">
+        <v>231</v>
+      </c>
+      <c r="K160">
+        <v>3</v>
+      </c>
+      <c r="L160" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161" t="s">
+        <v>154</v>
+      </c>
+      <c r="B161">
+        <v>6</v>
+      </c>
+      <c r="C161">
+        <v>6</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+      <c r="E161">
+        <v>90</v>
+      </c>
+      <c r="F161">
+        <v>10</v>
+      </c>
+      <c r="G161">
+        <v>10</v>
+      </c>
+      <c r="H161">
+        <v>10</v>
+      </c>
+      <c r="I161" t="s">
+        <v>109</v>
+      </c>
+      <c r="J161" t="s">
+        <v>102</v>
+      </c>
+      <c r="K161">
+        <v>3</v>
+      </c>
+      <c r="L161" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" t="s">
+        <v>221</v>
+      </c>
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162">
+        <v>6</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162">
+        <v>90</v>
+      </c>
+      <c r="F162">
+        <v>10</v>
+      </c>
+      <c r="G162">
+        <v>10</v>
+      </c>
+      <c r="H162">
+        <v>10</v>
+      </c>
+      <c r="I162" t="s">
+        <v>109</v>
+      </c>
+      <c r="J162" t="s">
+        <v>102</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" t="s">
+        <v>221</v>
+      </c>
+      <c r="B163">
+        <v>6</v>
+      </c>
+      <c r="C163">
+        <v>6</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+      <c r="E163">
+        <v>90</v>
+      </c>
+      <c r="F163">
+        <v>10</v>
+      </c>
+      <c r="G163">
+        <v>10</v>
+      </c>
+      <c r="H163">
+        <v>10</v>
+      </c>
+      <c r="I163" t="s">
+        <v>57</v>
+      </c>
+      <c r="J163" t="s">
+        <v>266</v>
+      </c>
+      <c r="K163">
+        <v>3</v>
+      </c>
+      <c r="L163" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164">
+        <v>6</v>
+      </c>
+      <c r="C164">
+        <v>4</v>
+      </c>
+      <c r="D164">
+        <v>2</v>
+      </c>
+      <c r="E164">
+        <v>90</v>
+      </c>
+      <c r="F164">
+        <v>10</v>
+      </c>
+      <c r="G164">
+        <v>10</v>
+      </c>
+      <c r="H164">
+        <v>10</v>
+      </c>
+      <c r="I164" t="s">
+        <v>57</v>
+      </c>
+      <c r="J164" t="s">
+        <v>131</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" t="s">
+        <v>36</v>
+      </c>
+      <c r="B165">
+        <v>6</v>
+      </c>
+      <c r="C165">
+        <v>4</v>
+      </c>
+      <c r="D165">
+        <v>2</v>
+      </c>
+      <c r="E165">
+        <v>90</v>
+      </c>
+      <c r="F165">
+        <v>10</v>
+      </c>
+      <c r="G165">
+        <v>10</v>
+      </c>
+      <c r="H165">
+        <v>10</v>
+      </c>
+      <c r="I165" t="s">
+        <v>58</v>
+      </c>
+      <c r="J165" t="s">
+        <v>231</v>
+      </c>
+      <c r="K165">
+        <v>3</v>
+      </c>
+      <c r="L165" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166" t="s">
+        <v>294</v>
+      </c>
+      <c r="B166">
+        <v>6</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166">
+        <v>2</v>
+      </c>
+      <c r="E166">
+        <v>90</v>
+      </c>
+      <c r="F166">
+        <v>10</v>
+      </c>
+      <c r="G166">
+        <v>10</v>
+      </c>
+      <c r="H166">
+        <v>10</v>
+      </c>
+      <c r="I166" t="s">
+        <v>109</v>
+      </c>
+      <c r="J166" t="s">
+        <v>295</v>
+      </c>
+      <c r="K166">
+        <v>3</v>
+      </c>
+      <c r="L166" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167" t="s">
+        <v>37</v>
+      </c>
+      <c r="B167">
+        <v>6</v>
+      </c>
+      <c r="C167">
+        <v>6</v>
+      </c>
+      <c r="D167">
+        <v>2</v>
+      </c>
+      <c r="E167">
+        <v>90</v>
+      </c>
+      <c r="F167">
+        <v>10</v>
+      </c>
+      <c r="G167">
+        <v>10</v>
+      </c>
+      <c r="H167">
+        <v>10</v>
+      </c>
+      <c r="I167" t="s">
+        <v>57</v>
+      </c>
+      <c r="J167" t="s">
+        <v>155</v>
+      </c>
+      <c r="K167">
+        <v>3</v>
+      </c>
+      <c r="L167" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168" t="s">
+        <v>37</v>
+      </c>
+      <c r="B168">
+        <v>6</v>
+      </c>
+      <c r="C168">
+        <v>6</v>
+      </c>
+      <c r="D168">
+        <v>2</v>
+      </c>
+      <c r="E168">
+        <v>90</v>
+      </c>
+      <c r="F168">
+        <v>10</v>
+      </c>
+      <c r="G168">
+        <v>10</v>
+      </c>
+      <c r="H168">
+        <v>10</v>
+      </c>
+      <c r="I168" t="s">
+        <v>58</v>
+      </c>
+      <c r="J168" t="s">
+        <v>237</v>
+      </c>
+      <c r="K168">
+        <v>3</v>
+      </c>
+      <c r="L168" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169" t="s">
+        <v>249</v>
+      </c>
+      <c r="B169">
+        <v>6</v>
+      </c>
+      <c r="C169">
+        <v>5</v>
+      </c>
+      <c r="D169">
+        <v>2</v>
+      </c>
+      <c r="E169">
+        <v>90</v>
+      </c>
+      <c r="F169">
+        <v>10</v>
+      </c>
+      <c r="G169">
+        <v>10</v>
+      </c>
+      <c r="H169">
+        <v>10</v>
+      </c>
+      <c r="I169" t="s">
+        <v>57</v>
+      </c>
+      <c r="J169" t="s">
+        <v>250</v>
+      </c>
+      <c r="K169">
+        <v>3</v>
+      </c>
+      <c r="L169" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" t="s">
+        <v>222</v>
+      </c>
+      <c r="B170">
+        <v>6</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170">
+        <v>2</v>
+      </c>
+      <c r="E170">
+        <v>90</v>
+      </c>
+      <c r="F170">
+        <v>10</v>
+      </c>
+      <c r="G170">
+        <v>10</v>
+      </c>
+      <c r="H170">
+        <v>10</v>
+      </c>
+      <c r="I170" t="s">
+        <v>57</v>
+      </c>
+      <c r="J170" t="s">
+        <v>251</v>
+      </c>
+      <c r="K170">
+        <v>3</v>
+      </c>
+      <c r="L170" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L143" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:L335" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
@@ -6944,18 +8071,18 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I144:I171" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I346:I373" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
       <formula1>"elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L177:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L379:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
       <formula1>"蓝色,绿色,灰色,红色,金色"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I143" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
-      <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E1048576" xr:uid="{067929F4-68AD-4FCF-9645-B8AA87BCECB2}">
       <formula1>0</formula1>
       <formula2>90</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I345" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
+      <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C1048576" xr:uid="{84D7772C-943A-4833-B43B-BB959E902FB7}">
       <formula1>1</formula1>
@@ -6969,7 +8096,7 @@
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L176" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L378" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
       <formula1>"blue,green,grey,red,yellow"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">
